--- a/backend/final_schedule.xlsx
+++ b/backend/final_schedule.xlsx
@@ -1605,13 +1605,13 @@
         <v>1</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>1999280.8</v>
+        <v>1999280</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>1999280.8</v>
+        <v>0</v>
       </c>
       <c r="K29" s="17" t="n">
-        <v>0.55759234</v>
+        <v>0</v>
       </c>
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="20" t="n">
@@ -1724,10 +1724,10 @@
         <v>300000</v>
       </c>
       <c r="J32" s="18" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="K32" s="17" t="n">
-        <v>0.08366897</v>
+        <v>0</v>
       </c>
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="20" t="n">
@@ -1784,10 +1784,10 @@
         <v>150000</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K33" s="17" t="n">
-        <v>0.04183449</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="20" t="n">
@@ -1900,10 +1900,10 @@
         <v>25000</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="K36" s="17" t="n">
-        <v>0.03486207</v>
+        <v>0</v>
       </c>
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="20" t="n">
@@ -1960,10 +1960,10 @@
         <v>60000</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>0.01673379</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="20" t="n">
@@ -2020,10 +2020,10 @@
         <v>68000</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>340000</v>
+        <v>0</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>0.09482483999999999</v>
+        <v>0</v>
       </c>
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="20" t="n">
@@ -2080,10 +2080,10 @@
         <v>35000</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>0.0488069</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="20" t="n">
@@ -2196,10 +2196,10 @@
         <v>800000</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="17" t="n">
-        <v>0.22311726</v>
+        <v>0</v>
       </c>
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="20" t="n">
@@ -2312,10 +2312,10 @@
         <v>1500000</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="K45" s="17" t="n">
-        <v>0.41834486</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="20" t="n">
@@ -2428,10 +2428,10 @@
         <v>85000</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="K48" s="17" t="n">
-        <v>0.02370621</v>
+        <v>0</v>
       </c>
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="20" t="n">
@@ -2472,10 +2472,10 @@
         <v>85000</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="K49" s="17" t="n">
-        <v>0.02370621</v>
+        <v>0</v>
       </c>
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="20" t="n">
@@ -2572,10 +2572,10 @@
         <v>5500</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>1140625.2</v>
+        <v>0</v>
       </c>
       <c r="K52" s="17" t="n">
-        <v>0.31811646</v>
+        <v>0</v>
       </c>
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="20" t="n">
@@ -2618,10 +2618,10 @@
         <v>255550</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>52997594.52</v>
+        <v>0</v>
       </c>
       <c r="K53" s="17" t="n">
-        <v>14.78084761</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="n"/>
@@ -2668,10 +2668,10 @@
         <v>26853</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>2684225.88</v>
+        <v>0</v>
       </c>
       <c r="K54" s="17" t="n">
-        <v>0.74862141</v>
+        <v>0</v>
       </c>
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="n"/>
@@ -2718,10 +2718,10 @@
         <v>61335</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>9363401.1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="17" t="n">
-        <v>2.6114205</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="n"/>
@@ -2768,10 +2768,10 @@
         <v>449902</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>5398824</v>
+        <v>0</v>
       </c>
       <c r="K56" s="17" t="n">
-        <v>1.50571352</v>
+        <v>0</v>
       </c>
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="20" t="n">
@@ -2814,10 +2814,10 @@
         <v>668187</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>8018244</v>
+        <v>0</v>
       </c>
       <c r="K57" s="17" t="n">
-        <v>2.23626079</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="17" t="n"/>
@@ -2864,10 +2864,10 @@
         <v>63699</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>191097</v>
+        <v>0</v>
       </c>
       <c r="K58" s="17" t="n">
-        <v>0.0532963</v>
+        <v>0</v>
       </c>
       <c r="L58" s="11" t="n"/>
       <c r="M58" s="17" t="n"/>
@@ -2970,10 +2970,10 @@
         <v>5500</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>791076</v>
+        <v>0</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>0.22062839</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="n"/>
       <c r="M61" s="20" t="n">
@@ -3016,10 +3016,10 @@
         <v>255550</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>36756267.6</v>
+        <v>0</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>10.25119715</v>
+        <v>0</v>
       </c>
       <c r="L62" s="11" t="n"/>
       <c r="M62" s="17" t="n"/>
@@ -3066,10 +3066,10 @@
         <v>26853</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>1828152.24</v>
+        <v>0</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>0.5098654</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="n"/>
       <c r="M63" s="17" t="n"/>
@@ -3116,10 +3116,10 @@
         <v>61335</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>6016350.15</v>
+        <v>0</v>
       </c>
       <c r="K64" s="17" t="n">
-        <v>1.67793945</v>
+        <v>0</v>
       </c>
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="17" t="n"/>
@@ -3166,10 +3166,10 @@
         <v>449902</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>3599216</v>
+        <v>0</v>
       </c>
       <c r="K65" s="17" t="n">
-        <v>1.00380902</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="n"/>
       <c r="M65" s="20" t="n">
@@ -3212,10 +3212,10 @@
         <v>668187</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>5345496</v>
+        <v>0</v>
       </c>
       <c r="K66" s="17" t="n">
-        <v>1.49084053</v>
+        <v>0</v>
       </c>
       <c r="L66" s="11" t="n"/>
       <c r="M66" s="17" t="n"/>
@@ -3262,10 +3262,10 @@
         <v>63699</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>127398</v>
+        <v>0</v>
       </c>
       <c r="K67" s="17" t="n">
-        <v>0.03553087</v>
+        <v>0</v>
       </c>
       <c r="L67" s="11" t="n"/>
       <c r="M67" s="17" t="n"/>
@@ -3400,10 +3400,10 @@
         <v>5500</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>27610</v>
+        <v>0</v>
       </c>
       <c r="K71" s="17" t="n">
-        <v>0.00770033</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="n"/>
       <c r="M71" s="17" t="n"/>
@@ -3444,10 +3444,10 @@
         <v>255550</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>1282861</v>
+        <v>0</v>
       </c>
       <c r="K72" s="17" t="n">
-        <v>0.35778554</v>
+        <v>0</v>
       </c>
       <c r="L72" s="11" t="n"/>
       <c r="M72" s="17" t="n"/>
@@ -3490,10 +3490,10 @@
         <v>26853</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>341033.1</v>
+        <v>0</v>
       </c>
       <c r="K73" s="17" t="n">
-        <v>0.09511296</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="n"/>
       <c r="M73" s="17" t="n"/>
@@ -3536,10 +3536,10 @@
         <v>61335</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>122670</v>
+        <v>0</v>
       </c>
       <c r="K74" s="17" t="n">
-        <v>0.03421224</v>
+        <v>0</v>
       </c>
       <c r="L74" s="11" t="n"/>
       <c r="M74" s="17" t="n"/>
@@ -3582,10 +3582,10 @@
         <v>449902</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>899804</v>
+        <v>0</v>
       </c>
       <c r="K75" s="17" t="n">
-        <v>0.25095225</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11" t="n"/>
       <c r="M75" s="17" t="n"/>
@@ -3628,10 +3628,10 @@
         <v>63699</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>127398</v>
+        <v>0</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>0.03553087</v>
+        <v>0</v>
       </c>
       <c r="L76" s="11" t="n"/>
       <c r="M76" s="17" t="n"/>
@@ -3730,10 +3730,10 @@
         <v>97486</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>1131081.315</v>
+        <v>0</v>
       </c>
       <c r="K79" s="17" t="n">
-        <v>0.31545471</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="n"/>
       <c r="M79" s="20" t="n">
@@ -3774,10 +3774,10 @@
         <v>5500</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>746620.875</v>
+        <v>0</v>
       </c>
       <c r="K80" s="17" t="n">
-        <v>0.20823001</v>
+        <v>0</v>
       </c>
       <c r="L80" s="11" t="n"/>
       <c r="M80" s="20" t="n">
@@ -3818,10 +3818,10 @@
         <v>255550</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>34690720.8375</v>
+        <v>0</v>
       </c>
       <c r="K81" s="17" t="n">
-        <v>9.675123230000001</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11" t="n"/>
       <c r="M81" s="17" t="n"/>
@@ -3866,10 +3866,10 @@
         <v>26853</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>1773372.12</v>
+        <v>0</v>
       </c>
       <c r="K82" s="17" t="n">
-        <v>0.49458741</v>
+        <v>0</v>
       </c>
       <c r="L82" s="11" t="n"/>
       <c r="M82" s="17" t="n"/>
@@ -3912,10 +3912,10 @@
         <v>61335</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>9923389.65</v>
+        <v>0</v>
       </c>
       <c r="K83" s="17" t="n">
-        <v>2.76759939</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="n"/>
       <c r="M83" s="17" t="n"/>
@@ -3960,10 +3960,10 @@
         <v>449902</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>3599216</v>
+        <v>0</v>
       </c>
       <c r="K84" s="17" t="n">
-        <v>1.00380902</v>
+        <v>0</v>
       </c>
       <c r="L84" s="11" t="n"/>
       <c r="M84" s="17" t="n"/>
@@ -4006,10 +4006,10 @@
         <v>668187</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>5345496</v>
+        <v>0</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>1.49084053</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="n"/>
       <c r="M85" s="17" t="n"/>
@@ -4052,10 +4052,10 @@
         <v>63699</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>127398</v>
+        <v>0</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>0.03553087</v>
+        <v>0</v>
       </c>
       <c r="L86" s="11" t="n"/>
       <c r="M86" s="17" t="n"/>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>Lantai 1</t>
+          <t>Lantai 2</t>
         </is>
       </c>
       <c r="D89" s="33" t="n"/>
@@ -4186,10 +4186,10 @@
         <v>5500</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>2277976.8</v>
+        <v>0</v>
       </c>
       <c r="K90" s="17" t="n">
-        <v>0.63531993</v>
+        <v>0</v>
       </c>
       <c r="L90" s="11" t="n"/>
       <c r="M90" s="17" t="n"/>
@@ -4230,10 +4230,10 @@
         <v>255550</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>61584381.18</v>
+        <v>0</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>17.175673</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="n"/>
       <c r="M91" s="17" t="n"/>
@@ -4282,10 +4282,10 @@
         <v>277206</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>48009307.14</v>
+        <v>0</v>
       </c>
       <c r="K92" s="17" t="n">
-        <v>13.38963134</v>
+        <v>0</v>
       </c>
       <c r="L92" s="11" t="n"/>
       <c r="M92" s="17" t="n"/>
@@ -4334,10 +4334,10 @@
         <v>26853</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>3335142.6</v>
+        <v>0</v>
       </c>
       <c r="K93" s="17" t="n">
-        <v>0.93015985</v>
+        <v>0</v>
       </c>
       <c r="L93" s="11" t="n"/>
       <c r="M93" s="17" t="n"/>
@@ -4386,10 +4386,10 @@
         <v>26853</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>5735263.74</v>
+        <v>0</v>
       </c>
       <c r="K94" s="17" t="n">
-        <v>1.59954542</v>
+        <v>0</v>
       </c>
       <c r="L94" s="11" t="n"/>
       <c r="M94" s="17" t="n"/>
@@ -4438,10 +4438,10 @@
         <v>449902</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>17546178</v>
+        <v>0</v>
       </c>
       <c r="K95" s="17" t="n">
-        <v>4.89356895</v>
+        <v>0</v>
       </c>
       <c r="L95" s="11" t="n"/>
       <c r="M95" s="17" t="n"/>
@@ -4486,10 +4486,10 @@
         <v>244459</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>3666885</v>
+        <v>0</v>
       </c>
       <c r="K96" s="17" t="n">
-        <v>1.02268167</v>
+        <v>0</v>
       </c>
       <c r="L96" s="11" t="n"/>
       <c r="M96" s="17" t="n"/>
@@ -4532,10 +4532,10 @@
         <v>668187</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>16036488</v>
+        <v>0</v>
       </c>
       <c r="K97" s="17" t="n">
-        <v>4.47252158</v>
+        <v>0</v>
       </c>
       <c r="L97" s="11" t="n"/>
       <c r="M97" s="17" t="n"/>
@@ -4578,10 +4578,10 @@
         <v>63699</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>254796</v>
+        <v>0</v>
       </c>
       <c r="K98" s="17" t="n">
-        <v>0.07106173</v>
+        <v>0</v>
       </c>
       <c r="L98" s="11" t="n"/>
       <c r="M98" s="17" t="n"/>
@@ -4624,10 +4624,10 @@
         <v>46759</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>93518</v>
+        <v>0</v>
       </c>
       <c r="K99" s="17" t="n">
-        <v>0.02608185</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11" t="n"/>
       <c r="M99" s="17" t="n"/>
@@ -5293,7 +5293,7 @@
         <v>2.312</v>
       </c>
       <c r="C2" s="52" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
@@ -5309,7 +5309,7 @@
         <v>8.943</v>
       </c>
       <c r="C3" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
@@ -5325,7 +5325,7 @@
         <v>25.422</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>99</v>
@@ -5341,7 +5341,7 @@
         <v>55.025</v>
       </c>
       <c r="C5" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5354,7 +5354,7 @@
         <v>72.816</v>
       </c>
       <c r="C6" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -5367,7 +5367,7 @@
         <v>83.726</v>
       </c>
       <c r="C7" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -5380,7 +5380,7 @@
         <v>94.53700000000001</v>
       </c>
       <c r="C8" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -5393,7 +5393,7 @@
         <v>98.81</v>
       </c>
       <c r="C9" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -5406,7 +5406,7 @@
         <v>100</v>
       </c>
       <c r="C10" s="52" t="n">
-        <v>0</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/backend/final_schedule.xlsx
+++ b/backend/final_schedule.xlsx
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>RP 397.997.000</t>
+          <t>RP 397.997</t>
         </is>
       </c>
     </row>
@@ -1608,39 +1608,29 @@
         <v>1999280</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>0</v>
+        <v>1999280</v>
       </c>
       <c r="K29" s="17" t="n">
-        <v>0</v>
+        <v>0.557592</v>
       </c>
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="20" t="n">
-        <v>0.0619547</v>
+        <v>0.06195467</v>
       </c>
       <c r="N29" s="20" t="n">
-        <v>0.0619547</v>
+        <v>0.06195467</v>
       </c>
       <c r="O29" s="20" t="n">
-        <v>0.0619547</v>
+        <v>0.06195467</v>
       </c>
       <c r="P29" s="20" t="n">
-        <v>0.0619547</v>
-      </c>
-      <c r="Q29" s="20" t="n">
-        <v>0.0619547</v>
-      </c>
-      <c r="R29" s="20" t="n">
-        <v>0.0619547</v>
-      </c>
-      <c r="S29" s="20" t="n">
-        <v>0.0619547</v>
-      </c>
-      <c r="T29" s="20" t="n">
-        <v>0.0619547</v>
-      </c>
-      <c r="U29" s="20" t="n">
-        <v>0.0619547</v>
-      </c>
+        <v>0.06195467</v>
+      </c>
+      <c r="Q29" s="17" t="n"/>
+      <c r="R29" s="17" t="n"/>
+      <c r="S29" s="17" t="n"/>
+      <c r="T29" s="17" t="n"/>
+      <c r="U29" s="17" t="n"/>
       <c r="V29" s="11" t="n"/>
       <c r="W29" s="19" t="n"/>
     </row>
@@ -1724,39 +1714,29 @@
         <v>300000</v>
       </c>
       <c r="J32" s="18" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="K32" s="17" t="n">
-        <v>0</v>
+        <v>0.08366899999999999</v>
       </c>
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="20" t="n">
-        <v>0.009296550000000001</v>
+        <v>0.009296560000000001</v>
       </c>
       <c r="N32" s="20" t="n">
-        <v>0.009296550000000001</v>
+        <v>0.009296560000000001</v>
       </c>
       <c r="O32" s="20" t="n">
-        <v>0.009296550000000001</v>
+        <v>0.009296560000000001</v>
       </c>
       <c r="P32" s="20" t="n">
-        <v>0.009296550000000001</v>
-      </c>
-      <c r="Q32" s="20" t="n">
-        <v>0.009296550000000001</v>
-      </c>
-      <c r="R32" s="20" t="n">
-        <v>0.009296550000000001</v>
-      </c>
-      <c r="S32" s="20" t="n">
-        <v>0.009296550000000001</v>
-      </c>
-      <c r="T32" s="20" t="n">
-        <v>0.009296550000000001</v>
-      </c>
-      <c r="U32" s="20" t="n">
-        <v>0.009296550000000001</v>
-      </c>
+        <v>0.009296560000000001</v>
+      </c>
+      <c r="Q32" s="17" t="n"/>
+      <c r="R32" s="17" t="n"/>
+      <c r="S32" s="17" t="n"/>
+      <c r="T32" s="17" t="n"/>
+      <c r="U32" s="17" t="n"/>
       <c r="V32" s="11" t="n"/>
       <c r="W32" s="19" t="n"/>
     </row>
@@ -1784,39 +1764,29 @@
         <v>150000</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="K33" s="17" t="n">
-        <v>0</v>
+        <v>0.041834</v>
       </c>
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="20" t="n">
-        <v>0.00464828</v>
+        <v>0.00464822</v>
       </c>
       <c r="N33" s="20" t="n">
-        <v>0.00464828</v>
+        <v>0.00464822</v>
       </c>
       <c r="O33" s="20" t="n">
-        <v>0.00464828</v>
+        <v>0.00464822</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.00464828</v>
-      </c>
-      <c r="Q33" s="20" t="n">
-        <v>0.00464828</v>
-      </c>
-      <c r="R33" s="20" t="n">
-        <v>0.00464828</v>
-      </c>
-      <c r="S33" s="20" t="n">
-        <v>0.00464828</v>
-      </c>
-      <c r="T33" s="20" t="n">
-        <v>0.00464828</v>
-      </c>
-      <c r="U33" s="20" t="n">
-        <v>0.00464828</v>
-      </c>
+        <v>0.00464822</v>
+      </c>
+      <c r="Q33" s="17" t="n"/>
+      <c r="R33" s="17" t="n"/>
+      <c r="S33" s="17" t="n"/>
+      <c r="T33" s="17" t="n"/>
+      <c r="U33" s="17" t="n"/>
       <c r="V33" s="11" t="n"/>
       <c r="W33" s="19" t="n"/>
     </row>
@@ -1900,10 +1870,10 @@
         <v>25000</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="K36" s="17" t="n">
-        <v>0</v>
+        <v>0.034862</v>
       </c>
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="20" t="n">
@@ -1918,21 +1888,11 @@
       <c r="P36" s="20" t="n">
         <v>0.00387356</v>
       </c>
-      <c r="Q36" s="20" t="n">
-        <v>0.00387356</v>
-      </c>
-      <c r="R36" s="20" t="n">
-        <v>0.00387356</v>
-      </c>
-      <c r="S36" s="20" t="n">
-        <v>0.00387356</v>
-      </c>
-      <c r="T36" s="20" t="n">
-        <v>0.00387356</v>
-      </c>
-      <c r="U36" s="20" t="n">
-        <v>0.00387356</v>
-      </c>
+      <c r="Q36" s="17" t="n"/>
+      <c r="R36" s="17" t="n"/>
+      <c r="S36" s="17" t="n"/>
+      <c r="T36" s="17" t="n"/>
+      <c r="U36" s="17" t="n"/>
       <c r="V36" s="11" t="n"/>
       <c r="W36" s="19" t="n"/>
     </row>
@@ -1960,39 +1920,29 @@
         <v>60000</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>0</v>
+        <v>0.016734</v>
       </c>
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="20" t="n">
-        <v>0.00185931</v>
+        <v>0.00185933</v>
       </c>
       <c r="N37" s="20" t="n">
-        <v>0.00185931</v>
+        <v>0.00185933</v>
       </c>
       <c r="O37" s="20" t="n">
-        <v>0.00185931</v>
+        <v>0.00185933</v>
       </c>
       <c r="P37" s="20" t="n">
-        <v>0.00185931</v>
-      </c>
-      <c r="Q37" s="20" t="n">
-        <v>0.00185931</v>
-      </c>
-      <c r="R37" s="20" t="n">
-        <v>0.00185931</v>
-      </c>
-      <c r="S37" s="20" t="n">
-        <v>0.00185931</v>
-      </c>
-      <c r="T37" s="20" t="n">
-        <v>0.00185931</v>
-      </c>
-      <c r="U37" s="20" t="n">
-        <v>0.00185931</v>
-      </c>
+        <v>0.00185933</v>
+      </c>
+      <c r="Q37" s="17" t="n"/>
+      <c r="R37" s="17" t="n"/>
+      <c r="S37" s="17" t="n"/>
+      <c r="T37" s="17" t="n"/>
+      <c r="U37" s="17" t="n"/>
       <c r="V37" s="11" t="n"/>
       <c r="W37" s="19" t="n"/>
     </row>
@@ -2020,39 +1970,29 @@
         <v>68000</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>0</v>
+        <v>0.09482500000000001</v>
       </c>
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="20" t="n">
-        <v>0.01053609</v>
+        <v>0.01053611</v>
       </c>
       <c r="N38" s="20" t="n">
-        <v>0.01053609</v>
+        <v>0.01053611</v>
       </c>
       <c r="O38" s="20" t="n">
-        <v>0.01053609</v>
+        <v>0.01053611</v>
       </c>
       <c r="P38" s="20" t="n">
-        <v>0.01053609</v>
-      </c>
-      <c r="Q38" s="20" t="n">
-        <v>0.01053609</v>
-      </c>
-      <c r="R38" s="20" t="n">
-        <v>0.01053609</v>
-      </c>
-      <c r="S38" s="20" t="n">
-        <v>0.01053609</v>
-      </c>
-      <c r="T38" s="20" t="n">
-        <v>0.01053609</v>
-      </c>
-      <c r="U38" s="20" t="n">
-        <v>0.01053609</v>
-      </c>
+        <v>0.01053611</v>
+      </c>
+      <c r="Q38" s="17" t="n"/>
+      <c r="R38" s="17" t="n"/>
+      <c r="S38" s="17" t="n"/>
+      <c r="T38" s="17" t="n"/>
+      <c r="U38" s="17" t="n"/>
       <c r="V38" s="11" t="n"/>
       <c r="W38" s="19" t="n"/>
     </row>
@@ -2080,39 +2020,29 @@
         <v>35000</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>0</v>
+        <v>0.048807</v>
       </c>
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="20" t="n">
-        <v>0.00542299</v>
+        <v>0.005423</v>
       </c>
       <c r="N39" s="20" t="n">
-        <v>0.00542299</v>
+        <v>0.005423</v>
       </c>
       <c r="O39" s="20" t="n">
-        <v>0.00542299</v>
+        <v>0.005423</v>
       </c>
       <c r="P39" s="20" t="n">
-        <v>0.00542299</v>
-      </c>
-      <c r="Q39" s="20" t="n">
-        <v>0.00542299</v>
-      </c>
-      <c r="R39" s="20" t="n">
-        <v>0.00542299</v>
-      </c>
-      <c r="S39" s="20" t="n">
-        <v>0.00542299</v>
-      </c>
-      <c r="T39" s="20" t="n">
-        <v>0.00542299</v>
-      </c>
-      <c r="U39" s="20" t="n">
-        <v>0.00542299</v>
-      </c>
+        <v>0.005423</v>
+      </c>
+      <c r="Q39" s="17" t="n"/>
+      <c r="R39" s="17" t="n"/>
+      <c r="S39" s="17" t="n"/>
+      <c r="T39" s="17" t="n"/>
+      <c r="U39" s="17" t="n"/>
       <c r="V39" s="11" t="n"/>
       <c r="W39" s="19" t="n"/>
     </row>
@@ -2196,39 +2126,29 @@
         <v>800000</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="K42" s="17" t="n">
-        <v>0</v>
+        <v>0.223117</v>
       </c>
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="20" t="n">
-        <v>0.02479081</v>
+        <v>0.02479078</v>
       </c>
       <c r="N42" s="20" t="n">
-        <v>0.02479081</v>
+        <v>0.02479078</v>
       </c>
       <c r="O42" s="20" t="n">
-        <v>0.02479081</v>
+        <v>0.02479078</v>
       </c>
       <c r="P42" s="20" t="n">
-        <v>0.02479081</v>
-      </c>
-      <c r="Q42" s="20" t="n">
-        <v>0.02479081</v>
-      </c>
-      <c r="R42" s="20" t="n">
-        <v>0.02479081</v>
-      </c>
-      <c r="S42" s="20" t="n">
-        <v>0.02479081</v>
-      </c>
-      <c r="T42" s="20" t="n">
-        <v>0.02479081</v>
-      </c>
-      <c r="U42" s="20" t="n">
-        <v>0.02479081</v>
-      </c>
+        <v>0.02479078</v>
+      </c>
+      <c r="Q42" s="17" t="n"/>
+      <c r="R42" s="17" t="n"/>
+      <c r="S42" s="17" t="n"/>
+      <c r="T42" s="17" t="n"/>
+      <c r="U42" s="17" t="n"/>
       <c r="V42" s="11" t="n"/>
       <c r="W42" s="19" t="n"/>
     </row>
@@ -2312,39 +2232,29 @@
         <v>1500000</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="K45" s="17" t="n">
-        <v>0</v>
+        <v>0.418345</v>
       </c>
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="20" t="n">
-        <v>0.04648276</v>
+        <v>0.04648278</v>
       </c>
       <c r="N45" s="20" t="n">
-        <v>0.04648276</v>
+        <v>0.04648278</v>
       </c>
       <c r="O45" s="20" t="n">
-        <v>0.04648276</v>
+        <v>0.04648278</v>
       </c>
       <c r="P45" s="20" t="n">
-        <v>0.04648276</v>
-      </c>
-      <c r="Q45" s="20" t="n">
-        <v>0.04648276</v>
-      </c>
-      <c r="R45" s="20" t="n">
-        <v>0.04648276</v>
-      </c>
-      <c r="S45" s="20" t="n">
-        <v>0.04648276</v>
-      </c>
-      <c r="T45" s="20" t="n">
-        <v>0.04648276</v>
-      </c>
-      <c r="U45" s="20" t="n">
-        <v>0.04648276</v>
-      </c>
+        <v>0.04648278</v>
+      </c>
+      <c r="Q45" s="17" t="n"/>
+      <c r="R45" s="17" t="n"/>
+      <c r="S45" s="17" t="n"/>
+      <c r="T45" s="17" t="n"/>
+      <c r="U45" s="17" t="n"/>
       <c r="V45" s="11" t="n"/>
       <c r="W45" s="19" t="n"/>
     </row>
@@ -2428,14 +2338,14 @@
         <v>85000</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="K48" s="17" t="n">
-        <v>0</v>
+        <v>0.023706</v>
       </c>
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="20" t="n">
-        <v>0.02370621</v>
+        <v>0.023706</v>
       </c>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="17" t="n"/>
@@ -2472,14 +2382,14 @@
         <v>85000</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="K49" s="17" t="n">
-        <v>0</v>
+        <v>0.023706</v>
       </c>
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="20" t="n">
-        <v>0.02370621</v>
+        <v>0.023706</v>
       </c>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="17" t="n"/>
@@ -2566,23 +2476,23 @@
         </is>
       </c>
       <c r="H52" s="17" t="n">
-        <v>207.3864</v>
+        <v>215.34</v>
       </c>
       <c r="I52" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>0</v>
+        <v>1184370</v>
       </c>
       <c r="K52" s="17" t="n">
-        <v>0</v>
+        <v>0.330317</v>
       </c>
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="20" t="n">
-        <v>0.15905823</v>
+        <v>0.159058</v>
       </c>
       <c r="N52" s="20" t="n">
-        <v>0.15905823</v>
+        <v>0.159058</v>
       </c>
       <c r="O52" s="17" t="n"/>
       <c r="P52" s="17" t="n"/>
@@ -2612,32 +2522,28 @@
         </is>
       </c>
       <c r="H53" s="17" t="n">
-        <v>207.3864</v>
+        <v>215.34</v>
       </c>
       <c r="I53" s="18" t="n">
         <v>255550</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>0</v>
+        <v>55030137</v>
       </c>
       <c r="K53" s="17" t="n">
-        <v>0</v>
+        <v>15.347717</v>
       </c>
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="n"/>
       <c r="N53" s="17" t="n"/>
       <c r="O53" s="20" t="n">
-        <v>3.6952119</v>
+        <v>3.695212</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>3.6952119</v>
-      </c>
-      <c r="Q53" s="20" t="n">
-        <v>3.6952119</v>
-      </c>
-      <c r="R53" s="20" t="n">
-        <v>3.6952119</v>
-      </c>
+        <v>3.695212</v>
+      </c>
+      <c r="Q53" s="17" t="n"/>
+      <c r="R53" s="17" t="n"/>
       <c r="S53" s="17" t="n"/>
       <c r="T53" s="17" t="n"/>
       <c r="U53" s="17" t="n"/>
@@ -2662,32 +2568,28 @@
         </is>
       </c>
       <c r="H54" s="17" t="n">
-        <v>99.95999999999999</v>
+        <v>102.06</v>
       </c>
       <c r="I54" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>0</v>
+        <v>2740617.18</v>
       </c>
       <c r="K54" s="17" t="n">
-        <v>0</v>
+        <v>0.7643489999999999</v>
       </c>
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="n"/>
       <c r="N54" s="17" t="n"/>
       <c r="O54" s="20" t="n">
-        <v>0.18715535</v>
+        <v>0.18715525</v>
       </c>
       <c r="P54" s="20" t="n">
-        <v>0.18715535</v>
-      </c>
-      <c r="Q54" s="20" t="n">
-        <v>0.18715535</v>
-      </c>
-      <c r="R54" s="20" t="n">
-        <v>0.18715535</v>
-      </c>
+        <v>0.18715525</v>
+      </c>
+      <c r="Q54" s="17" t="n"/>
+      <c r="R54" s="17" t="n"/>
       <c r="S54" s="17" t="n"/>
       <c r="T54" s="17" t="n"/>
       <c r="U54" s="17" t="n"/>
@@ -2718,25 +2620,23 @@
         <v>61335</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>0</v>
+        <v>9363401.1</v>
       </c>
       <c r="K55" s="17" t="n">
-        <v>0</v>
+        <v>2.61142</v>
       </c>
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="n"/>
       <c r="N55" s="20" t="n">
-        <v>0.65285512</v>
+        <v>0.652855</v>
       </c>
       <c r="O55" s="20" t="n">
-        <v>0.65285512</v>
+        <v>0.652855</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>0.65285512</v>
-      </c>
-      <c r="Q55" s="20" t="n">
-        <v>0.65285512</v>
-      </c>
+        <v>0.652855</v>
+      </c>
+      <c r="Q55" s="17" t="n"/>
       <c r="R55" s="17" t="n"/>
       <c r="S55" s="17" t="n"/>
       <c r="T55" s="17" t="n"/>
@@ -2762,7 +2662,7 @@
         </is>
       </c>
       <c r="H56" s="17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I56" s="18" t="n">
         <v>449902</v>
@@ -2775,10 +2675,10 @@
       </c>
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="20" t="n">
-        <v>0.75285676</v>
+        <v>0.752857</v>
       </c>
       <c r="N56" s="20" t="n">
-        <v>0.75285676</v>
+        <v>0.752857</v>
       </c>
       <c r="O56" s="17" t="n"/>
       <c r="P56" s="17" t="n"/>
@@ -2814,28 +2714,20 @@
         <v>668187</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>0</v>
+        <v>8018244</v>
       </c>
       <c r="K57" s="17" t="n">
-        <v>0</v>
+        <v>2.236261</v>
       </c>
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="17" t="n"/>
       <c r="N57" s="17" t="n"/>
       <c r="O57" s="17" t="n"/>
       <c r="P57" s="17" t="n"/>
-      <c r="Q57" s="20" t="n">
-        <v>0.5590652</v>
-      </c>
-      <c r="R57" s="20" t="n">
-        <v>0.5590652</v>
-      </c>
-      <c r="S57" s="20" t="n">
-        <v>0.5590652</v>
-      </c>
-      <c r="T57" s="20" t="n">
-        <v>0.5590652</v>
-      </c>
+      <c r="Q57" s="17" t="n"/>
+      <c r="R57" s="17" t="n"/>
+      <c r="S57" s="17" t="n"/>
+      <c r="T57" s="17" t="n"/>
       <c r="U57" s="17" t="n"/>
       <c r="V57" s="11" t="n"/>
       <c r="W57" s="19" t="n"/>
@@ -2864,28 +2756,20 @@
         <v>63699</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>0</v>
+        <v>191097</v>
       </c>
       <c r="K58" s="17" t="n">
-        <v>0</v>
+        <v>0.053296</v>
       </c>
       <c r="L58" s="11" t="n"/>
       <c r="M58" s="17" t="n"/>
       <c r="N58" s="17" t="n"/>
       <c r="O58" s="17" t="n"/>
       <c r="P58" s="17" t="n"/>
-      <c r="Q58" s="20" t="n">
-        <v>0.01332407</v>
-      </c>
-      <c r="R58" s="20" t="n">
-        <v>0.01332407</v>
-      </c>
-      <c r="S58" s="20" t="n">
-        <v>0.01332407</v>
-      </c>
-      <c r="T58" s="20" t="n">
-        <v>0.01332407</v>
-      </c>
+      <c r="Q58" s="17" t="n"/>
+      <c r="R58" s="17" t="n"/>
+      <c r="S58" s="17" t="n"/>
+      <c r="T58" s="17" t="n"/>
       <c r="U58" s="17" t="n"/>
       <c r="V58" s="11" t="n"/>
       <c r="W58" s="19" t="n"/>
@@ -2970,17 +2854,17 @@
         <v>5500</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>0</v>
+        <v>791076</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>0</v>
+        <v>0.220628</v>
       </c>
       <c r="L61" s="11" t="n"/>
       <c r="M61" s="20" t="n">
-        <v>0.1103142</v>
+        <v>0.110314</v>
       </c>
       <c r="N61" s="20" t="n">
-        <v>0.1103142</v>
+        <v>0.110314</v>
       </c>
       <c r="O61" s="17" t="n"/>
       <c r="P61" s="17" t="n"/>
@@ -3016,26 +2900,22 @@
         <v>255550</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>0</v>
+        <v>36756267.6</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>0</v>
+        <v>10.251197</v>
       </c>
       <c r="L62" s="11" t="n"/>
       <c r="M62" s="17" t="n"/>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="20" t="n">
-        <v>1.70853286</v>
+        <v>1.70853283</v>
       </c>
       <c r="P62" s="20" t="n">
-        <v>3.41706572</v>
-      </c>
-      <c r="Q62" s="20" t="n">
-        <v>3.41706572</v>
-      </c>
-      <c r="R62" s="20" t="n">
-        <v>1.70853285</v>
-      </c>
+        <v>3.41706567</v>
+      </c>
+      <c r="Q62" s="17" t="n"/>
+      <c r="R62" s="17" t="n"/>
       <c r="S62" s="17" t="n"/>
       <c r="T62" s="17" t="n"/>
       <c r="U62" s="17" t="n"/>
@@ -3066,26 +2946,22 @@
         <v>26853</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>0</v>
+        <v>1828152.24</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>0</v>
+        <v>0.509865</v>
       </c>
       <c r="L63" s="11" t="n"/>
       <c r="M63" s="17" t="n"/>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="20" t="n">
-        <v>0.12746635</v>
+        <v>0.12746625</v>
       </c>
       <c r="P63" s="20" t="n">
-        <v>0.12746635</v>
-      </c>
-      <c r="Q63" s="20" t="n">
-        <v>0.12746635</v>
-      </c>
-      <c r="R63" s="20" t="n">
-        <v>0.12746635</v>
-      </c>
+        <v>0.12746625</v>
+      </c>
+      <c r="Q63" s="17" t="n"/>
+      <c r="R63" s="17" t="n"/>
       <c r="S63" s="17" t="n"/>
       <c r="T63" s="17" t="n"/>
       <c r="U63" s="17" t="n"/>
@@ -3116,10 +2992,10 @@
         <v>61335</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>0</v>
+        <v>6016350.15</v>
       </c>
       <c r="K64" s="17" t="n">
-        <v>0</v>
+        <v>1.677939</v>
       </c>
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="17" t="n"/>
@@ -3132,9 +3008,7 @@
       <c r="P64" s="20" t="n">
         <v>0.5159792</v>
       </c>
-      <c r="Q64" s="20" t="n">
-        <v>0.13000185</v>
-      </c>
+      <c r="Q64" s="17" t="n"/>
       <c r="R64" s="17" t="n"/>
       <c r="S64" s="17" t="n"/>
       <c r="T64" s="17" t="n"/>
@@ -3160,7 +3034,7 @@
         </is>
       </c>
       <c r="H65" s="17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I65" s="18" t="n">
         <v>449902</v>
@@ -3176,7 +3050,7 @@
         <v>0.55015167</v>
       </c>
       <c r="N65" s="20" t="n">
-        <v>0.45365735</v>
+        <v>0.45365733</v>
       </c>
       <c r="O65" s="17" t="n"/>
       <c r="P65" s="17" t="n"/>
@@ -3212,28 +3086,20 @@
         <v>668187</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>0</v>
+        <v>5345496</v>
       </c>
       <c r="K66" s="17" t="n">
-        <v>0</v>
+        <v>1.490841</v>
       </c>
       <c r="L66" s="11" t="n"/>
       <c r="M66" s="17" t="n"/>
       <c r="N66" s="17" t="n"/>
       <c r="O66" s="17" t="n"/>
       <c r="P66" s="17" t="n"/>
-      <c r="Q66" s="20" t="n">
-        <v>0.37271013</v>
-      </c>
-      <c r="R66" s="20" t="n">
-        <v>0.37271013</v>
-      </c>
-      <c r="S66" s="20" t="n">
-        <v>0.37271013</v>
-      </c>
-      <c r="T66" s="20" t="n">
-        <v>0.37271013</v>
-      </c>
+      <c r="Q66" s="17" t="n"/>
+      <c r="R66" s="17" t="n"/>
+      <c r="S66" s="17" t="n"/>
+      <c r="T66" s="17" t="n"/>
       <c r="U66" s="17" t="n"/>
       <c r="V66" s="11" t="n"/>
       <c r="W66" s="19" t="n"/>
@@ -3262,28 +3128,20 @@
         <v>63699</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>0</v>
+        <v>127398</v>
       </c>
       <c r="K67" s="17" t="n">
-        <v>0</v>
+        <v>0.035531</v>
       </c>
       <c r="L67" s="11" t="n"/>
       <c r="M67" s="17" t="n"/>
       <c r="N67" s="17" t="n"/>
       <c r="O67" s="17" t="n"/>
       <c r="P67" s="17" t="n"/>
-      <c r="Q67" s="20" t="n">
-        <v>0.00888272</v>
-      </c>
-      <c r="R67" s="20" t="n">
-        <v>0.00888272</v>
-      </c>
-      <c r="S67" s="20" t="n">
-        <v>0.00888272</v>
-      </c>
-      <c r="T67" s="20" t="n">
-        <v>0.00888272</v>
-      </c>
+      <c r="Q67" s="17" t="n"/>
+      <c r="R67" s="17" t="n"/>
+      <c r="S67" s="17" t="n"/>
+      <c r="T67" s="17" t="n"/>
       <c r="U67" s="17" t="n"/>
       <c r="V67" s="11" t="n"/>
       <c r="W67" s="19" t="n"/>
@@ -3400,10 +3258,10 @@
         <v>5500</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>0</v>
+        <v>27610</v>
       </c>
       <c r="K71" s="17" t="n">
-        <v>0</v>
+        <v>0.0077</v>
       </c>
       <c r="L71" s="11" t="n"/>
       <c r="M71" s="17" t="n"/>
@@ -3413,9 +3271,7 @@
       <c r="Q71" s="17" t="n"/>
       <c r="R71" s="17" t="n"/>
       <c r="S71" s="17" t="n"/>
-      <c r="T71" s="20" t="n">
-        <v>0.00770033</v>
-      </c>
+      <c r="T71" s="17" t="n"/>
       <c r="U71" s="17" t="n"/>
       <c r="V71" s="11" t="n"/>
       <c r="W71" s="19" t="n"/>
@@ -3444,10 +3300,10 @@
         <v>255550</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>0</v>
+        <v>1282861</v>
       </c>
       <c r="K72" s="17" t="n">
-        <v>0</v>
+        <v>0.357786</v>
       </c>
       <c r="L72" s="11" t="n"/>
       <c r="M72" s="17" t="n"/>
@@ -3457,12 +3313,8 @@
       <c r="Q72" s="17" t="n"/>
       <c r="R72" s="17" t="n"/>
       <c r="S72" s="17" t="n"/>
-      <c r="T72" s="20" t="n">
-        <v>0.23852369</v>
-      </c>
-      <c r="U72" s="20" t="n">
-        <v>0.11926185</v>
-      </c>
+      <c r="T72" s="17" t="n"/>
+      <c r="U72" s="17" t="n"/>
       <c r="V72" s="11" t="n"/>
       <c r="W72" s="19" t="n"/>
     </row>
@@ -3490,10 +3342,10 @@
         <v>26853</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>0</v>
+        <v>341033.1</v>
       </c>
       <c r="K73" s="17" t="n">
-        <v>0</v>
+        <v>0.095113</v>
       </c>
       <c r="L73" s="11" t="n"/>
       <c r="M73" s="17" t="n"/>
@@ -3503,12 +3355,8 @@
       <c r="Q73" s="17" t="n"/>
       <c r="R73" s="17" t="n"/>
       <c r="S73" s="17" t="n"/>
-      <c r="T73" s="20" t="n">
-        <v>0.06340864</v>
-      </c>
-      <c r="U73" s="20" t="n">
-        <v>0.03170432</v>
-      </c>
+      <c r="T73" s="17" t="n"/>
+      <c r="U73" s="17" t="n"/>
       <c r="V73" s="11" t="n"/>
       <c r="W73" s="19" t="n"/>
     </row>
@@ -3536,10 +3384,10 @@
         <v>61335</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>0</v>
+        <v>122670</v>
       </c>
       <c r="K74" s="17" t="n">
-        <v>0</v>
+        <v>0.034212</v>
       </c>
       <c r="L74" s="11" t="n"/>
       <c r="M74" s="17" t="n"/>
@@ -3549,12 +3397,8 @@
       <c r="Q74" s="17" t="n"/>
       <c r="R74" s="17" t="n"/>
       <c r="S74" s="17" t="n"/>
-      <c r="T74" s="20" t="n">
-        <v>0.02280816</v>
-      </c>
-      <c r="U74" s="20" t="n">
-        <v>0.01140408</v>
-      </c>
+      <c r="T74" s="17" t="n"/>
+      <c r="U74" s="17" t="n"/>
       <c r="V74" s="11" t="n"/>
       <c r="W74" s="19" t="n"/>
     </row>
@@ -3582,10 +3426,10 @@
         <v>449902</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>0</v>
+        <v>899804</v>
       </c>
       <c r="K75" s="17" t="n">
-        <v>0</v>
+        <v>0.250952</v>
       </c>
       <c r="L75" s="11" t="n"/>
       <c r="M75" s="17" t="n"/>
@@ -3595,12 +3439,8 @@
       <c r="Q75" s="17" t="n"/>
       <c r="R75" s="17" t="n"/>
       <c r="S75" s="17" t="n"/>
-      <c r="T75" s="20" t="n">
-        <v>0.1673015</v>
-      </c>
-      <c r="U75" s="20" t="n">
-        <v>0.08365075</v>
-      </c>
+      <c r="T75" s="17" t="n"/>
+      <c r="U75" s="17" t="n"/>
       <c r="V75" s="11" t="n"/>
       <c r="W75" s="19" t="n"/>
     </row>
@@ -3628,10 +3468,10 @@
         <v>63699</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>0</v>
+        <v>127398</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>0</v>
+        <v>0.035531</v>
       </c>
       <c r="L76" s="11" t="n"/>
       <c r="M76" s="17" t="n"/>
@@ -3641,12 +3481,8 @@
       <c r="Q76" s="17" t="n"/>
       <c r="R76" s="17" t="n"/>
       <c r="S76" s="17" t="n"/>
-      <c r="T76" s="20" t="n">
-        <v>0.02368725</v>
-      </c>
-      <c r="U76" s="20" t="n">
-        <v>0.01184362</v>
-      </c>
+      <c r="T76" s="17" t="n"/>
+      <c r="U76" s="17" t="n"/>
       <c r="V76" s="11" t="n"/>
       <c r="W76" s="19" t="n"/>
     </row>
@@ -3730,14 +3566,14 @@
         <v>97486</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>0</v>
+        <v>1131081.315</v>
       </c>
       <c r="K79" s="17" t="n">
-        <v>0</v>
+        <v>0.315455</v>
       </c>
       <c r="L79" s="11" t="n"/>
       <c r="M79" s="20" t="n">
-        <v>0.31545471</v>
+        <v>0.315455</v>
       </c>
       <c r="N79" s="17" t="n"/>
       <c r="O79" s="17" t="n"/>
@@ -3768,20 +3604,20 @@
         </is>
       </c>
       <c r="H80" s="17" t="n">
-        <v>135.74925</v>
+        <v>67.87462499999999</v>
       </c>
       <c r="I80" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>0</v>
+        <v>373310.4374999999</v>
       </c>
       <c r="K80" s="17" t="n">
-        <v>0</v>
+        <v>0.104115</v>
       </c>
       <c r="L80" s="11" t="n"/>
       <c r="M80" s="20" t="n">
-        <v>0.20823001</v>
+        <v>0.20823</v>
       </c>
       <c r="N80" s="17" t="n"/>
       <c r="O80" s="17" t="n"/>
@@ -3812,27 +3648,27 @@
         </is>
       </c>
       <c r="H81" s="17" t="n">
-        <v>135.74925</v>
+        <v>67.87462499999999</v>
       </c>
       <c r="I81" s="18" t="n">
         <v>255550</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0</v>
+        <v>17345360.41875</v>
       </c>
       <c r="K81" s="17" t="n">
-        <v>0</v>
+        <v>4.837562</v>
       </c>
       <c r="L81" s="11" t="n"/>
       <c r="M81" s="17" t="n"/>
       <c r="N81" s="20" t="n">
-        <v>1.2093904</v>
+        <v>1.20939038</v>
       </c>
       <c r="O81" s="20" t="n">
-        <v>4.7893144</v>
+        <v>4.78931444</v>
       </c>
       <c r="P81" s="20" t="n">
-        <v>3.67641843</v>
+        <v>3.67641818</v>
       </c>
       <c r="Q81" s="17" t="n"/>
       <c r="R81" s="17" t="n"/>
@@ -3860,24 +3696,24 @@
         </is>
       </c>
       <c r="H82" s="17" t="n">
-        <v>66.04000000000001</v>
+        <v>33.02</v>
       </c>
       <c r="I82" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>0</v>
+        <v>886686.0600000001</v>
       </c>
       <c r="K82" s="17" t="n">
-        <v>0</v>
+        <v>0.247294</v>
       </c>
       <c r="L82" s="11" t="n"/>
       <c r="M82" s="17" t="n"/>
       <c r="N82" s="20" t="n">
-        <v>0.24729371</v>
+        <v>0.2472935</v>
       </c>
       <c r="O82" s="20" t="n">
-        <v>0.24729371</v>
+        <v>0.2472935</v>
       </c>
       <c r="P82" s="17" t="n"/>
       <c r="Q82" s="17" t="n"/>
@@ -3912,25 +3748,19 @@
         <v>61335</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>0</v>
+        <v>9923389.65</v>
       </c>
       <c r="K83" s="17" t="n">
-        <v>0</v>
+        <v>2.767599</v>
       </c>
       <c r="L83" s="11" t="n"/>
       <c r="M83" s="17" t="n"/>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n"/>
       <c r="P83" s="17" t="n"/>
-      <c r="Q83" s="20" t="n">
-        <v>0.18450663</v>
-      </c>
-      <c r="R83" s="20" t="n">
-        <v>0.34594992</v>
-      </c>
-      <c r="S83" s="20" t="n">
-        <v>2.23714284</v>
-      </c>
+      <c r="Q83" s="17" t="n"/>
+      <c r="R83" s="17" t="n"/>
+      <c r="S83" s="17" t="n"/>
       <c r="T83" s="17" t="n"/>
       <c r="U83" s="17" t="n"/>
       <c r="V83" s="11" t="n"/>
@@ -3954,7 +3784,7 @@
         </is>
       </c>
       <c r="H84" s="17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I84" s="18" t="n">
         <v>449902</v>
@@ -3968,10 +3798,10 @@
       <c r="L84" s="11" t="n"/>
       <c r="M84" s="17" t="n"/>
       <c r="N84" s="20" t="n">
-        <v>0.50190451</v>
+        <v>0.5019045</v>
       </c>
       <c r="O84" s="20" t="n">
-        <v>0.50190451</v>
+        <v>0.5019045</v>
       </c>
       <c r="P84" s="17" t="n"/>
       <c r="Q84" s="17" t="n"/>
@@ -4000,16 +3830,16 @@
         </is>
       </c>
       <c r="H85" s="17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I85" s="18" t="n">
         <v>668187</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>0</v>
+        <v>2672748</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>0</v>
+        <v>0.74542</v>
       </c>
       <c r="L85" s="11" t="n"/>
       <c r="M85" s="17" t="n"/>
@@ -4019,12 +3849,8 @@
       <c r="Q85" s="17" t="n"/>
       <c r="R85" s="17" t="n"/>
       <c r="S85" s="17" t="n"/>
-      <c r="T85" s="20" t="n">
-        <v>0.74542027</v>
-      </c>
-      <c r="U85" s="20" t="n">
-        <v>0.74542027</v>
-      </c>
+      <c r="T85" s="17" t="n"/>
+      <c r="U85" s="17" t="n"/>
       <c r="V85" s="11" t="n"/>
       <c r="W85" s="19" t="n"/>
     </row>
@@ -4046,16 +3872,16 @@
         </is>
       </c>
       <c r="H86" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="18" t="n">
         <v>63699</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>0</v>
+        <v>63699</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>0</v>
+        <v>0.017765</v>
       </c>
       <c r="L86" s="11" t="n"/>
       <c r="M86" s="17" t="n"/>
@@ -4065,12 +3891,8 @@
       <c r="Q86" s="17" t="n"/>
       <c r="R86" s="17" t="n"/>
       <c r="S86" s="17" t="n"/>
-      <c r="T86" s="20" t="n">
-        <v>0.01776544</v>
-      </c>
-      <c r="U86" s="20" t="n">
-        <v>0.01776544</v>
-      </c>
+      <c r="T86" s="17" t="n"/>
+      <c r="U86" s="17" t="n"/>
       <c r="V86" s="11" t="n"/>
       <c r="W86" s="19" t="n"/>
     </row>
@@ -4138,7 +3960,7 @@
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>Lantai 2</t>
+          <t>Lantai 1</t>
         </is>
       </c>
       <c r="D89" s="33" t="n"/>
@@ -4180,21 +4002,21 @@
         </is>
       </c>
       <c r="H90" s="17" t="n">
-        <v>414.1776</v>
+        <v>572.822</v>
       </c>
       <c r="I90" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>0</v>
+        <v>3150521</v>
       </c>
       <c r="K90" s="17" t="n">
-        <v>0</v>
+        <v>0.87867</v>
       </c>
       <c r="L90" s="11" t="n"/>
       <c r="M90" s="17" t="n"/>
       <c r="N90" s="20" t="n">
-        <v>0.63531993</v>
+        <v>0.63532</v>
       </c>
       <c r="O90" s="17" t="n"/>
       <c r="P90" s="17" t="n"/>
@@ -4224,16 +4046,16 @@
         </is>
       </c>
       <c r="H91" s="17" t="n">
-        <v>240.9876</v>
+        <v>297.18</v>
       </c>
       <c r="I91" s="18" t="n">
         <v>255550</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>0</v>
+        <v>75944349</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>0</v>
+        <v>21.180619</v>
       </c>
       <c r="L91" s="11" t="n"/>
       <c r="M91" s="17" t="n"/>
@@ -4244,15 +4066,9 @@
       <c r="P91" s="20" t="n">
         <v>5.18136414</v>
       </c>
-      <c r="Q91" s="20" t="n">
-        <v>4.29391825</v>
-      </c>
-      <c r="R91" s="20" t="n">
-        <v>3.37309326</v>
-      </c>
-      <c r="S91" s="20" t="n">
-        <v>3.37309329</v>
-      </c>
+      <c r="Q91" s="17" t="n"/>
+      <c r="R91" s="17" t="n"/>
+      <c r="S91" s="17" t="n"/>
       <c r="T91" s="17" t="n"/>
       <c r="U91" s="17" t="n"/>
       <c r="V91" s="11" t="n"/>
@@ -4276,35 +4092,29 @@
         </is>
       </c>
       <c r="H92" s="17" t="n">
-        <v>173.19</v>
+        <v>275.642</v>
       </c>
       <c r="I92" s="18" t="n">
         <v>277206</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>0</v>
+        <v>76409616.252</v>
       </c>
       <c r="K92" s="17" t="n">
-        <v>0</v>
+        <v>21.31038</v>
       </c>
       <c r="L92" s="11" t="n"/>
       <c r="M92" s="17" t="n"/>
       <c r="N92" s="17" t="n"/>
       <c r="O92" s="20" t="n">
-        <v>0.74386841</v>
+        <v>0.74386839</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>9.23160521</v>
-      </c>
-      <c r="Q92" s="20" t="n">
-        <v>3.34740784</v>
-      </c>
-      <c r="R92" s="20" t="n">
-        <v>0.03337494</v>
-      </c>
-      <c r="S92" s="20" t="n">
-        <v>0.03337494</v>
-      </c>
+        <v>9.231605220000001</v>
+      </c>
+      <c r="Q92" s="17" t="n"/>
+      <c r="R92" s="17" t="n"/>
+      <c r="S92" s="17" t="n"/>
       <c r="T92" s="17" t="n"/>
       <c r="U92" s="17" t="n"/>
       <c r="V92" s="11" t="n"/>
@@ -4328,35 +4138,29 @@
         </is>
       </c>
       <c r="H93" s="17" t="n">
-        <v>124.2</v>
+        <v>154.2</v>
       </c>
       <c r="I93" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>0</v>
+        <v>4140732.6</v>
       </c>
       <c r="K93" s="17" t="n">
-        <v>0</v>
+        <v>1.154836</v>
       </c>
       <c r="L93" s="11" t="n"/>
       <c r="M93" s="17" t="n"/>
       <c r="N93" s="17" t="n"/>
       <c r="O93" s="20" t="n">
-        <v>0.15502664</v>
+        <v>0.15502667</v>
       </c>
       <c r="P93" s="20" t="n">
-        <v>0.31005328</v>
-      </c>
-      <c r="Q93" s="20" t="n">
-        <v>0.23253996</v>
-      </c>
-      <c r="R93" s="20" t="n">
-        <v>0.11626999</v>
-      </c>
-      <c r="S93" s="20" t="n">
-        <v>0.11626999</v>
-      </c>
+        <v>0.31005333</v>
+      </c>
+      <c r="Q93" s="17" t="n"/>
+      <c r="R93" s="17" t="n"/>
+      <c r="S93" s="17" t="n"/>
       <c r="T93" s="17" t="n"/>
       <c r="U93" s="17" t="n"/>
       <c r="V93" s="11" t="n"/>
@@ -4380,35 +4184,29 @@
         </is>
       </c>
       <c r="H94" s="17" t="n">
-        <v>213.58</v>
+        <v>267.6554554</v>
       </c>
       <c r="I94" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>0</v>
+        <v>7187351.9438562</v>
       </c>
       <c r="K94" s="17" t="n">
-        <v>0</v>
+        <v>2.004528</v>
       </c>
       <c r="L94" s="11" t="n"/>
       <c r="M94" s="17" t="n"/>
       <c r="N94" s="17" t="n"/>
       <c r="O94" s="20" t="n">
-        <v>0.39988636</v>
+        <v>0.39988625</v>
       </c>
       <c r="P94" s="20" t="n">
-        <v>0.39988636</v>
-      </c>
-      <c r="Q94" s="20" t="n">
-        <v>0.39988636</v>
-      </c>
-      <c r="R94" s="20" t="n">
-        <v>0.19994317</v>
-      </c>
-      <c r="S94" s="20" t="n">
-        <v>0.19994317</v>
-      </c>
+        <v>0.39988625</v>
+      </c>
+      <c r="Q94" s="17" t="n"/>
+      <c r="R94" s="17" t="n"/>
+      <c r="S94" s="17" t="n"/>
       <c r="T94" s="17" t="n"/>
       <c r="U94" s="17" t="n"/>
       <c r="V94" s="11" t="n"/>
@@ -4432,27 +4230,27 @@
         </is>
       </c>
       <c r="H95" s="17" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I95" s="18" t="n">
         <v>449902</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>0</v>
+        <v>6298628</v>
       </c>
       <c r="K95" s="17" t="n">
-        <v>0</v>
+        <v>1.756666</v>
       </c>
       <c r="L95" s="11" t="n"/>
       <c r="M95" s="17" t="n"/>
       <c r="N95" s="20" t="n">
-        <v>1.22339224</v>
+        <v>1.22339225</v>
       </c>
       <c r="O95" s="20" t="n">
-        <v>1.63118965</v>
+        <v>1.63118967</v>
       </c>
       <c r="P95" s="20" t="n">
-        <v>2.03898706</v>
+        <v>2.03898708</v>
       </c>
       <c r="Q95" s="17" t="n"/>
       <c r="R95" s="17" t="n"/>
@@ -4480,16 +4278,16 @@
         </is>
       </c>
       <c r="H96" s="17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I96" s="18" t="n">
         <v>244459</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>0</v>
+        <v>3422426</v>
       </c>
       <c r="K96" s="17" t="n">
-        <v>0</v>
+        <v>0.954503</v>
       </c>
       <c r="L96" s="11" t="n"/>
       <c r="M96" s="17" t="n"/>
@@ -4498,12 +4296,8 @@
       <c r="P96" s="17" t="n"/>
       <c r="Q96" s="17" t="n"/>
       <c r="R96" s="17" t="n"/>
-      <c r="S96" s="20" t="n">
-        <v>0.68178778</v>
-      </c>
-      <c r="T96" s="20" t="n">
-        <v>0.34089389</v>
-      </c>
+      <c r="S96" s="17" t="n"/>
+      <c r="T96" s="17" t="n"/>
       <c r="U96" s="17" t="n"/>
       <c r="V96" s="11" t="n"/>
       <c r="W96" s="19" t="n"/>
@@ -4526,16 +4320,16 @@
         </is>
       </c>
       <c r="H97" s="17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I97" s="18" t="n">
         <v>668187</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>0</v>
+        <v>13363740</v>
       </c>
       <c r="K97" s="17" t="n">
-        <v>0</v>
+        <v>3.727101</v>
       </c>
       <c r="L97" s="11" t="n"/>
       <c r="M97" s="17" t="n"/>
@@ -4544,12 +4338,8 @@
       <c r="P97" s="17" t="n"/>
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="17" t="n"/>
-      <c r="S97" s="20" t="n">
-        <v>2.98168105</v>
-      </c>
-      <c r="T97" s="20" t="n">
-        <v>1.49084053</v>
-      </c>
+      <c r="S97" s="17" t="n"/>
+      <c r="T97" s="17" t="n"/>
       <c r="U97" s="17" t="n"/>
       <c r="V97" s="11" t="n"/>
       <c r="W97" s="19" t="n"/>
@@ -4572,16 +4362,16 @@
         </is>
       </c>
       <c r="H98" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I98" s="18" t="n">
         <v>63699</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>0</v>
+        <v>382194</v>
       </c>
       <c r="K98" s="17" t="n">
-        <v>0</v>
+        <v>0.106593</v>
       </c>
       <c r="L98" s="11" t="n"/>
       <c r="M98" s="17" t="n"/>
@@ -4590,12 +4380,8 @@
       <c r="P98" s="17" t="n"/>
       <c r="Q98" s="17" t="n"/>
       <c r="R98" s="17" t="n"/>
-      <c r="S98" s="20" t="n">
-        <v>0.04737449</v>
-      </c>
-      <c r="T98" s="20" t="n">
-        <v>0.02368724</v>
-      </c>
+      <c r="S98" s="17" t="n"/>
+      <c r="T98" s="17" t="n"/>
       <c r="U98" s="17" t="n"/>
       <c r="V98" s="11" t="n"/>
       <c r="W98" s="19" t="n"/>
@@ -4618,16 +4404,16 @@
         </is>
       </c>
       <c r="H99" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="18" t="n">
         <v>46759</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>0</v>
+        <v>46759</v>
       </c>
       <c r="K99" s="17" t="n">
-        <v>0</v>
+        <v>0.013041</v>
       </c>
       <c r="L99" s="11" t="n"/>
       <c r="M99" s="17" t="n"/>
@@ -4636,12 +4422,8 @@
       <c r="P99" s="17" t="n"/>
       <c r="Q99" s="17" t="n"/>
       <c r="R99" s="17" t="n"/>
-      <c r="S99" s="20" t="n">
-        <v>0.0173879</v>
-      </c>
-      <c r="T99" s="20" t="n">
-        <v>0.008693950000000001</v>
-      </c>
+      <c r="S99" s="17" t="n"/>
+      <c r="T99" s="17" t="n"/>
       <c r="U99" s="17" t="n"/>
       <c r="V99" s="11" t="n"/>
       <c r="W99" s="19" t="n"/>
@@ -5293,7 +5075,7 @@
         <v>2.312</v>
       </c>
       <c r="C2" s="52" t="n">
-        <v>7.06</v>
+        <v>7.252</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
@@ -5309,7 +5091,7 @@
         <v>8.943</v>
       </c>
       <c r="C3" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
@@ -5325,7 +5107,7 @@
         <v>25.422</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>28.684</v>
       </c>
       <c r="F4" t="n">
         <v>99</v>
@@ -5341,7 +5123,7 @@
         <v>55.025</v>
       </c>
       <c r="C5" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>77.035</v>
       </c>
     </row>
     <row r="6">
@@ -5351,10 +5133,10 @@
         </is>
       </c>
       <c r="B6" s="52" t="n">
-        <v>72.816</v>
+        <v>55.025</v>
       </c>
       <c r="C6" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>73.06100000000001</v>
       </c>
     </row>
     <row r="7">
@@ -5364,10 +5146,10 @@
         </is>
       </c>
       <c r="B7" s="52" t="n">
-        <v>83.726</v>
+        <v>55.025</v>
       </c>
       <c r="C7" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>73.06100000000001</v>
       </c>
     </row>
     <row r="8">
@@ -5377,10 +5159,10 @@
         </is>
       </c>
       <c r="B8" s="52" t="n">
-        <v>94.53700000000001</v>
+        <v>55.025</v>
       </c>
       <c r="C8" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>73.06100000000001</v>
       </c>
     </row>
     <row r="9">
@@ -5390,10 +5172,10 @@
         </is>
       </c>
       <c r="B9" s="52" t="n">
-        <v>98.81</v>
+        <v>55.025</v>
       </c>
       <c r="C9" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>73.06100000000001</v>
       </c>
     </row>
     <row r="10">
@@ -5403,10 +5185,10 @@
         </is>
       </c>
       <c r="B10" s="52" t="n">
-        <v>100</v>
+        <v>55.025</v>
       </c>
       <c r="C10" s="52" t="n">
-        <v>9.726000000000001</v>
+        <v>73.06100000000001</v>
       </c>
     </row>
   </sheetData>

--- a/backend/final_schedule.xlsx
+++ b/backend/final_schedule.xlsx
@@ -132,20 +132,6 @@
     </border>
     <border>
       <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom style="thin"/>
@@ -165,11 +151,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -253,33 +253,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -289,8 +280,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,33 +433,6 @@
             </numRef>
           </val>
           <smooth val="1"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'CHART_DATA'!$A$2:$A$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'CHART_DATA'!$C$2:$C$10</f>
-            </numRef>
-          </val>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -893,7 +861,7 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="15" customWidth="1" min="23" max="23"/>
@@ -1145,9 +1113,9 @@
           <t>URAIAN</t>
         </is>
       </c>
-      <c r="D19" s="33" t="n"/>
-      <c r="E19" s="33" t="n"/>
-      <c r="F19" s="34" t="n"/>
+      <c r="D19" s="47" t="n"/>
+      <c r="E19" s="47" t="n"/>
+      <c r="F19" s="48" t="n"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
           <t>SATUAN</t>
@@ -1179,14 +1147,14 @@
           <t>WAKTU PELAKSANAAN 60 HARI KALENDER</t>
         </is>
       </c>
-      <c r="N19" s="42" t="n"/>
-      <c r="O19" s="42" t="n"/>
-      <c r="P19" s="42" t="n"/>
-      <c r="Q19" s="42" t="n"/>
-      <c r="R19" s="42" t="n"/>
-      <c r="S19" s="42" t="n"/>
-      <c r="T19" s="42" t="n"/>
-      <c r="U19" s="43" t="n"/>
+      <c r="N19" s="33" t="n"/>
+      <c r="O19" s="33" t="n"/>
+      <c r="P19" s="33" t="n"/>
+      <c r="Q19" s="33" t="n"/>
+      <c r="R19" s="33" t="n"/>
+      <c r="S19" s="33" t="n"/>
+      <c r="T19" s="33" t="n"/>
+      <c r="U19" s="49" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="5" t="inlineStr">
         <is>
@@ -1196,8 +1164,8 @@
     </row>
     <row r="20">
       <c r="B20" s="29" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="F20" s="47" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="F20" s="40" t="n"/>
       <c r="G20" s="29" t="n"/>
       <c r="H20" s="29" t="n"/>
       <c r="I20" s="29" t="n"/>
@@ -1209,17 +1177,17 @@
           <t>BULAN 1</t>
         </is>
       </c>
-      <c r="N20" s="42" t="n"/>
-      <c r="O20" s="42" t="n"/>
-      <c r="P20" s="43" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="49" t="n"/>
       <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>BULAN 2</t>
         </is>
       </c>
-      <c r="R20" s="42" t="n"/>
-      <c r="S20" s="42" t="n"/>
-      <c r="T20" s="43" t="n"/>
+      <c r="R20" s="33" t="n"/>
+      <c r="S20" s="33" t="n"/>
+      <c r="T20" s="49" t="n"/>
       <c r="U20" s="5" t="inlineStr">
         <is>
           <t>BULAN 3</t>
@@ -1230,8 +1198,8 @@
     </row>
     <row r="21">
       <c r="B21" s="29" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="F21" s="47" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="F21" s="40" t="n"/>
       <c r="G21" s="29" t="n"/>
       <c r="H21" s="29" t="n"/>
       <c r="I21" s="29" t="n"/>
@@ -1288,8 +1256,8 @@
     </row>
     <row r="22">
       <c r="B22" s="29" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="F22" s="47" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="F22" s="40" t="n"/>
       <c r="G22" s="29" t="n"/>
       <c r="H22" s="29" t="n"/>
       <c r="I22" s="29" t="n"/>
@@ -1346,15 +1314,15 @@
     </row>
     <row r="23">
       <c r="B23" s="29" t="n"/>
-      <c r="C23" s="51" t="n"/>
+      <c r="C23" s="44" t="n"/>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="30" t="n"/>
-      <c r="F23" s="37" t="n"/>
-      <c r="G23" s="45" t="n"/>
-      <c r="H23" s="45" t="n"/>
-      <c r="I23" s="45" t="n"/>
-      <c r="J23" s="45" t="n"/>
-      <c r="K23" s="45" t="n"/>
+      <c r="F23" s="45" t="n"/>
+      <c r="G23" s="38" t="n"/>
+      <c r="H23" s="38" t="n"/>
+      <c r="I23" s="38" t="n"/>
+      <c r="J23" s="38" t="n"/>
+      <c r="K23" s="38" t="n"/>
       <c r="L23" s="29" t="n"/>
       <c r="M23" s="5" t="inlineStr">
         <is>
@@ -1405,13 +1373,13 @@
       <c r="W23" s="29" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="45" t="n"/>
+      <c r="B24" s="38" t="n"/>
       <c r="C24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="42" t="n"/>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="43" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="49" t="n"/>
       <c r="G24" s="5" t="n">
         <v>2</v>
       </c>
@@ -1456,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="V24" s="29" t="n"/>
-      <c r="W24" s="45" t="n"/>
+      <c r="W24" s="38" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="7" t="n"/>
@@ -1493,9 +1461,9 @@
           <t>PEKERJAAN SMKK</t>
         </is>
       </c>
-      <c r="D26" s="33" t="n"/>
-      <c r="E26" s="33" t="n"/>
-      <c r="F26" s="34" t="n"/>
+      <c r="D26" s="47" t="n"/>
+      <c r="E26" s="47" t="n"/>
+      <c r="F26" s="48" t="n"/>
       <c r="G26" s="13" t="n"/>
       <c r="H26" s="13" t="n"/>
       <c r="I26" s="13" t="n"/>
@@ -1523,9 +1491,9 @@
           <t>Penyelenggaraan Keamanan dan Kesehatan Kerja serta Keselamatan Konstruksi</t>
         </is>
       </c>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="34" t="n"/>
+      <c r="D27" s="47" t="n"/>
+      <c r="E27" s="47" t="n"/>
+      <c r="F27" s="48" t="n"/>
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="17" t="n">
         <v>0</v>
@@ -1563,9 +1531,9 @@
           <t>PENYIAPAN SMKK</t>
         </is>
       </c>
-      <c r="D28" s="33" t="n"/>
-      <c r="E28" s="33" t="n"/>
-      <c r="F28" s="34" t="n"/>
+      <c r="D28" s="47" t="n"/>
+      <c r="E28" s="47" t="n"/>
+      <c r="F28" s="48" t="n"/>
       <c r="G28" s="13" t="n"/>
       <c r="H28" s="13" t="n"/>
       <c r="I28" s="13" t="n"/>
@@ -1593,9 +1561,9 @@
           <t>Pembuatan Prosedur dan instruksi kerja</t>
         </is>
       </c>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="33" t="n"/>
-      <c r="F29" s="34" t="n"/>
+      <c r="D29" s="47" t="n"/>
+      <c r="E29" s="47" t="n"/>
+      <c r="F29" s="48" t="n"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Set</t>
@@ -1626,11 +1594,21 @@
       <c r="P29" s="20" t="n">
         <v>0.06195467</v>
       </c>
-      <c r="Q29" s="17" t="n"/>
-      <c r="R29" s="17" t="n"/>
-      <c r="S29" s="17" t="n"/>
-      <c r="T29" s="17" t="n"/>
-      <c r="U29" s="17" t="n"/>
+      <c r="Q29" s="20" t="n">
+        <v>0.06195467</v>
+      </c>
+      <c r="R29" s="20" t="n">
+        <v>0.06195467</v>
+      </c>
+      <c r="S29" s="20" t="n">
+        <v>0.06195467</v>
+      </c>
+      <c r="T29" s="20" t="n">
+        <v>0.06195467</v>
+      </c>
+      <c r="U29" s="20" t="n">
+        <v>0.06195467</v>
+      </c>
       <c r="V29" s="11" t="n"/>
       <c r="W29" s="19" t="n"/>
     </row>
@@ -1669,9 +1647,9 @@
           <t>SOSIALISASI DAN PROMOSI SMKK</t>
         </is>
       </c>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="33" t="n"/>
-      <c r="F31" s="34" t="n"/>
+      <c r="D31" s="47" t="n"/>
+      <c r="E31" s="47" t="n"/>
+      <c r="F31" s="48" t="n"/>
       <c r="G31" s="13" t="n"/>
       <c r="H31" s="13" t="n"/>
       <c r="I31" s="13" t="n"/>
@@ -1699,9 +1677,9 @@
           <t>Spanduk (banner) ; (6m2)</t>
         </is>
       </c>
-      <c r="D32" s="33" t="n"/>
-      <c r="E32" s="33" t="n"/>
-      <c r="F32" s="34" t="n"/>
+      <c r="D32" s="47" t="n"/>
+      <c r="E32" s="47" t="n"/>
+      <c r="F32" s="48" t="n"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
@@ -1732,11 +1710,21 @@
       <c r="P32" s="20" t="n">
         <v>0.009296560000000001</v>
       </c>
-      <c r="Q32" s="17" t="n"/>
-      <c r="R32" s="17" t="n"/>
-      <c r="S32" s="17" t="n"/>
-      <c r="T32" s="17" t="n"/>
-      <c r="U32" s="17" t="n"/>
+      <c r="Q32" s="20" t="n">
+        <v>0.009296560000000001</v>
+      </c>
+      <c r="R32" s="20" t="n">
+        <v>0.009296560000000001</v>
+      </c>
+      <c r="S32" s="20" t="n">
+        <v>0.009296560000000001</v>
+      </c>
+      <c r="T32" s="20" t="n">
+        <v>0.009296560000000001</v>
+      </c>
+      <c r="U32" s="20" t="n">
+        <v>0.009296560000000001</v>
+      </c>
       <c r="V32" s="11" t="n"/>
       <c r="W32" s="19" t="n"/>
     </row>
@@ -1749,9 +1737,9 @@
           <t>Poster</t>
         </is>
       </c>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="34" t="n"/>
+      <c r="D33" s="47" t="n"/>
+      <c r="E33" s="47" t="n"/>
+      <c r="F33" s="48" t="n"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Bh</t>
@@ -1782,11 +1770,21 @@
       <c r="P33" s="20" t="n">
         <v>0.00464822</v>
       </c>
-      <c r="Q33" s="17" t="n"/>
-      <c r="R33" s="17" t="n"/>
-      <c r="S33" s="17" t="n"/>
-      <c r="T33" s="17" t="n"/>
-      <c r="U33" s="17" t="n"/>
+      <c r="Q33" s="20" t="n">
+        <v>0.00464822</v>
+      </c>
+      <c r="R33" s="20" t="n">
+        <v>0.00464822</v>
+      </c>
+      <c r="S33" s="20" t="n">
+        <v>0.00464822</v>
+      </c>
+      <c r="T33" s="20" t="n">
+        <v>0.00464822</v>
+      </c>
+      <c r="U33" s="20" t="n">
+        <v>0.00464822</v>
+      </c>
       <c r="V33" s="11" t="n"/>
       <c r="W33" s="19" t="n"/>
     </row>
@@ -1825,9 +1823,9 @@
           <t>ALAT PELINDUNG KERJA DAN ALAT PELINDUNG DIRI</t>
         </is>
       </c>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="34" t="n"/>
+      <c r="D35" s="47" t="n"/>
+      <c r="E35" s="47" t="n"/>
+      <c r="F35" s="48" t="n"/>
       <c r="G35" s="13" t="n"/>
       <c r="H35" s="13" t="n"/>
       <c r="I35" s="13" t="n"/>
@@ -1855,9 +1853,9 @@
           <t>Topi Pelindung (Safety Helmet)</t>
         </is>
       </c>
-      <c r="D36" s="33" t="n"/>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="34" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="48" t="n"/>
       <c r="G36" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -1888,11 +1886,21 @@
       <c r="P36" s="20" t="n">
         <v>0.00387356</v>
       </c>
-      <c r="Q36" s="17" t="n"/>
-      <c r="R36" s="17" t="n"/>
-      <c r="S36" s="17" t="n"/>
-      <c r="T36" s="17" t="n"/>
-      <c r="U36" s="17" t="n"/>
+      <c r="Q36" s="20" t="n">
+        <v>0.00387356</v>
+      </c>
+      <c r="R36" s="20" t="n">
+        <v>0.00387356</v>
+      </c>
+      <c r="S36" s="20" t="n">
+        <v>0.00387356</v>
+      </c>
+      <c r="T36" s="20" t="n">
+        <v>0.00387356</v>
+      </c>
+      <c r="U36" s="20" t="n">
+        <v>0.00387356</v>
+      </c>
       <c r="V36" s="11" t="n"/>
       <c r="W36" s="19" t="n"/>
     </row>
@@ -1905,9 +1913,9 @@
           <t>Pelindung pernafasan dan mulut (Masker)</t>
         </is>
       </c>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="34" t="n"/>
+      <c r="D37" s="47" t="n"/>
+      <c r="E37" s="47" t="n"/>
+      <c r="F37" s="48" t="n"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Kotak</t>
@@ -1938,11 +1946,21 @@
       <c r="P37" s="20" t="n">
         <v>0.00185933</v>
       </c>
-      <c r="Q37" s="17" t="n"/>
-      <c r="R37" s="17" t="n"/>
-      <c r="S37" s="17" t="n"/>
-      <c r="T37" s="17" t="n"/>
-      <c r="U37" s="17" t="n"/>
+      <c r="Q37" s="20" t="n">
+        <v>0.00185933</v>
+      </c>
+      <c r="R37" s="20" t="n">
+        <v>0.00185933</v>
+      </c>
+      <c r="S37" s="20" t="n">
+        <v>0.00185933</v>
+      </c>
+      <c r="T37" s="20" t="n">
+        <v>0.00185933</v>
+      </c>
+      <c r="U37" s="20" t="n">
+        <v>0.00185933</v>
+      </c>
       <c r="V37" s="11" t="n"/>
       <c r="W37" s="19" t="n"/>
     </row>
@@ -1955,9 +1973,9 @@
           <t>Sepatu keselamatan (Rubber safety shoes and toe cap)</t>
         </is>
       </c>
-      <c r="D38" s="33" t="n"/>
-      <c r="E38" s="33" t="n"/>
-      <c r="F38" s="34" t="n"/>
+      <c r="D38" s="47" t="n"/>
+      <c r="E38" s="47" t="n"/>
+      <c r="F38" s="48" t="n"/>
       <c r="G38" s="7" t="inlineStr">
         <is>
           <t>Psg</t>
@@ -1988,11 +2006,21 @@
       <c r="P38" s="20" t="n">
         <v>0.01053611</v>
       </c>
-      <c r="Q38" s="17" t="n"/>
-      <c r="R38" s="17" t="n"/>
-      <c r="S38" s="17" t="n"/>
-      <c r="T38" s="17" t="n"/>
-      <c r="U38" s="17" t="n"/>
+      <c r="Q38" s="20" t="n">
+        <v>0.01053611</v>
+      </c>
+      <c r="R38" s="20" t="n">
+        <v>0.01053611</v>
+      </c>
+      <c r="S38" s="20" t="n">
+        <v>0.01053611</v>
+      </c>
+      <c r="T38" s="20" t="n">
+        <v>0.01053611</v>
+      </c>
+      <c r="U38" s="20" t="n">
+        <v>0.01053611</v>
+      </c>
       <c r="V38" s="11" t="n"/>
       <c r="W38" s="19" t="n"/>
     </row>
@@ -2005,9 +2033,9 @@
           <t>Rompi keselamatan (safety vest)</t>
         </is>
       </c>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="33" t="n"/>
-      <c r="F39" s="34" t="n"/>
+      <c r="D39" s="47" t="n"/>
+      <c r="E39" s="47" t="n"/>
+      <c r="F39" s="48" t="n"/>
       <c r="G39" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -2038,11 +2066,21 @@
       <c r="P39" s="20" t="n">
         <v>0.005423</v>
       </c>
-      <c r="Q39" s="17" t="n"/>
-      <c r="R39" s="17" t="n"/>
-      <c r="S39" s="17" t="n"/>
-      <c r="T39" s="17" t="n"/>
-      <c r="U39" s="17" t="n"/>
+      <c r="Q39" s="20" t="n">
+        <v>0.005423</v>
+      </c>
+      <c r="R39" s="20" t="n">
+        <v>0.005423</v>
+      </c>
+      <c r="S39" s="20" t="n">
+        <v>0.005423</v>
+      </c>
+      <c r="T39" s="20" t="n">
+        <v>0.005423</v>
+      </c>
+      <c r="U39" s="20" t="n">
+        <v>0.005423</v>
+      </c>
       <c r="V39" s="11" t="n"/>
       <c r="W39" s="19" t="n"/>
     </row>
@@ -2081,9 +2119,9 @@
           <t>ASURANSI DAN PERIZINAN</t>
         </is>
       </c>
-      <c r="D41" s="33" t="n"/>
-      <c r="E41" s="33" t="n"/>
-      <c r="F41" s="34" t="n"/>
+      <c r="D41" s="47" t="n"/>
+      <c r="E41" s="47" t="n"/>
+      <c r="F41" s="48" t="n"/>
       <c r="G41" s="13" t="n"/>
       <c r="H41" s="13" t="n"/>
       <c r="I41" s="13" t="n"/>
@@ -2111,9 +2149,9 @@
           <t>BPJS  Ketenagakerjaan</t>
         </is>
       </c>
-      <c r="D42" s="33" t="n"/>
-      <c r="E42" s="33" t="n"/>
-      <c r="F42" s="34" t="n"/>
+      <c r="D42" s="47" t="n"/>
+      <c r="E42" s="47" t="n"/>
+      <c r="F42" s="48" t="n"/>
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>Ls</t>
@@ -2144,11 +2182,21 @@
       <c r="P42" s="20" t="n">
         <v>0.02479078</v>
       </c>
-      <c r="Q42" s="17" t="n"/>
-      <c r="R42" s="17" t="n"/>
-      <c r="S42" s="17" t="n"/>
-      <c r="T42" s="17" t="n"/>
-      <c r="U42" s="17" t="n"/>
+      <c r="Q42" s="20" t="n">
+        <v>0.02479078</v>
+      </c>
+      <c r="R42" s="20" t="n">
+        <v>0.02479078</v>
+      </c>
+      <c r="S42" s="20" t="n">
+        <v>0.02479078</v>
+      </c>
+      <c r="T42" s="20" t="n">
+        <v>0.02479078</v>
+      </c>
+      <c r="U42" s="20" t="n">
+        <v>0.02479078</v>
+      </c>
       <c r="V42" s="11" t="n"/>
       <c r="W42" s="19" t="n"/>
     </row>
@@ -2187,9 +2235,9 @@
           <t xml:space="preserve">FASILITAS, SARANA DAN PRASARANA KESEHATAN </t>
         </is>
       </c>
-      <c r="D44" s="33" t="n"/>
-      <c r="E44" s="33" t="n"/>
-      <c r="F44" s="34" t="n"/>
+      <c r="D44" s="47" t="n"/>
+      <c r="E44" s="47" t="n"/>
+      <c r="F44" s="48" t="n"/>
       <c r="G44" s="13" t="n"/>
       <c r="H44" s="13" t="n"/>
       <c r="I44" s="13" t="n"/>
@@ -2217,9 +2265,9 @@
           <t>Peralatan K3 (Kotak P3k, Obat Luka, Perban, Dll)</t>
         </is>
       </c>
-      <c r="D45" s="33" t="n"/>
-      <c r="E45" s="33" t="n"/>
-      <c r="F45" s="34" t="n"/>
+      <c r="D45" s="47" t="n"/>
+      <c r="E45" s="47" t="n"/>
+      <c r="F45" s="48" t="n"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
           <t>Ls</t>
@@ -2250,11 +2298,21 @@
       <c r="P45" s="20" t="n">
         <v>0.04648278</v>
       </c>
-      <c r="Q45" s="17" t="n"/>
-      <c r="R45" s="17" t="n"/>
-      <c r="S45" s="17" t="n"/>
-      <c r="T45" s="17" t="n"/>
-      <c r="U45" s="17" t="n"/>
+      <c r="Q45" s="20" t="n">
+        <v>0.04648278</v>
+      </c>
+      <c r="R45" s="20" t="n">
+        <v>0.04648278</v>
+      </c>
+      <c r="S45" s="20" t="n">
+        <v>0.04648278</v>
+      </c>
+      <c r="T45" s="20" t="n">
+        <v>0.04648278</v>
+      </c>
+      <c r="U45" s="20" t="n">
+        <v>0.04648278</v>
+      </c>
       <c r="V45" s="11" t="n"/>
       <c r="W45" s="19" t="n"/>
     </row>
@@ -2293,9 +2351,9 @@
           <t>RAMBU-RAMBU YANG DIPERLUKAN</t>
         </is>
       </c>
-      <c r="D47" s="33" t="n"/>
-      <c r="E47" s="33" t="n"/>
-      <c r="F47" s="34" t="n"/>
+      <c r="D47" s="47" t="n"/>
+      <c r="E47" s="47" t="n"/>
+      <c r="F47" s="48" t="n"/>
       <c r="G47" s="13" t="n"/>
       <c r="H47" s="13" t="n"/>
       <c r="I47" s="13" t="n"/>
@@ -2323,9 +2381,9 @@
           <t>Rambu petunjuk</t>
         </is>
       </c>
-      <c r="D48" s="33" t="n"/>
-      <c r="E48" s="33" t="n"/>
-      <c r="F48" s="34" t="n"/>
+      <c r="D48" s="47" t="n"/>
+      <c r="E48" s="47" t="n"/>
+      <c r="F48" s="48" t="n"/>
       <c r="G48" s="7" t="inlineStr">
         <is>
           <t>Bh</t>
@@ -2367,9 +2425,9 @@
           <t>Rambu peringatan</t>
         </is>
       </c>
-      <c r="D49" s="33" t="n"/>
-      <c r="E49" s="33" t="n"/>
-      <c r="F49" s="34" t="n"/>
+      <c r="D49" s="47" t="n"/>
+      <c r="E49" s="47" t="n"/>
+      <c r="F49" s="48" t="n"/>
       <c r="G49" s="7" t="inlineStr">
         <is>
           <t>Bh</t>
@@ -2437,9 +2495,9 @@
           <t>GEDUNG KELAS I (LANTAI 2)</t>
         </is>
       </c>
-      <c r="D51" s="33" t="n"/>
-      <c r="E51" s="33" t="n"/>
-      <c r="F51" s="34" t="n"/>
+      <c r="D51" s="47" t="n"/>
+      <c r="E51" s="47" t="n"/>
+      <c r="F51" s="48" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="13" t="n"/>
       <c r="I51" s="13" t="n"/>
@@ -2467,25 +2525,25 @@
           <t>Pek. Bongkaran plafond</t>
         </is>
       </c>
-      <c r="D52" s="33" t="n"/>
-      <c r="E52" s="33" t="n"/>
-      <c r="F52" s="34" t="n"/>
+      <c r="D52" s="47" t="n"/>
+      <c r="E52" s="47" t="n"/>
+      <c r="F52" s="48" t="n"/>
       <c r="G52" s="7" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
       <c r="H52" s="17" t="n">
-        <v>215.34</v>
+        <v>207.3864</v>
       </c>
       <c r="I52" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>1184370</v>
+        <v>1140625.2</v>
       </c>
       <c r="K52" s="17" t="n">
-        <v>0.330317</v>
+        <v>0.318116</v>
       </c>
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="20" t="n">
@@ -2513,25 +2571,25 @@
           <t>Pek. Pas. Plafond PVC Putih Polos</t>
         </is>
       </c>
-      <c r="D53" s="33" t="n"/>
-      <c r="E53" s="33" t="n"/>
-      <c r="F53" s="34" t="n"/>
+      <c r="D53" s="47" t="n"/>
+      <c r="E53" s="47" t="n"/>
+      <c r="F53" s="48" t="n"/>
       <c r="G53" s="7" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
       <c r="H53" s="17" t="n">
-        <v>215.34</v>
+        <v>207.3864</v>
       </c>
       <c r="I53" s="18" t="n">
         <v>255550</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>55030137</v>
+        <v>52997594.52</v>
       </c>
       <c r="K53" s="17" t="n">
-        <v>15.347717</v>
+        <v>14.780848</v>
       </c>
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="n"/>
@@ -2542,8 +2600,12 @@
       <c r="P53" s="20" t="n">
         <v>3.695212</v>
       </c>
-      <c r="Q53" s="17" t="n"/>
-      <c r="R53" s="17" t="n"/>
+      <c r="Q53" s="20" t="n">
+        <v>3.695212</v>
+      </c>
+      <c r="R53" s="20" t="n">
+        <v>3.695212</v>
+      </c>
       <c r="S53" s="17" t="n"/>
       <c r="T53" s="17" t="n"/>
       <c r="U53" s="17" t="n"/>
@@ -2559,25 +2621,25 @@
           <t>Pek. List Plafond PVC Putih</t>
         </is>
       </c>
-      <c r="D54" s="33" t="n"/>
-      <c r="E54" s="33" t="n"/>
-      <c r="F54" s="34" t="n"/>
+      <c r="D54" s="47" t="n"/>
+      <c r="E54" s="47" t="n"/>
+      <c r="F54" s="48" t="n"/>
       <c r="G54" s="7" t="inlineStr">
         <is>
           <t>m'</t>
         </is>
       </c>
       <c r="H54" s="17" t="n">
-        <v>102.06</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="I54" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>2740617.18</v>
+        <v>2684225.88</v>
       </c>
       <c r="K54" s="17" t="n">
-        <v>0.7643489999999999</v>
+        <v>0.748621</v>
       </c>
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="n"/>
@@ -2588,8 +2650,12 @@
       <c r="P54" s="20" t="n">
         <v>0.18715525</v>
       </c>
-      <c r="Q54" s="17" t="n"/>
-      <c r="R54" s="17" t="n"/>
+      <c r="Q54" s="20" t="n">
+        <v>0.18715525</v>
+      </c>
+      <c r="R54" s="20" t="n">
+        <v>0.18715525</v>
+      </c>
       <c r="S54" s="17" t="n"/>
       <c r="T54" s="17" t="n"/>
       <c r="U54" s="17" t="n"/>
@@ -2605,9 +2671,9 @@
           <t>Pek. Pengecatan Plafond</t>
         </is>
       </c>
-      <c r="D55" s="33" t="n"/>
-      <c r="E55" s="33" t="n"/>
-      <c r="F55" s="34" t="n"/>
+      <c r="D55" s="47" t="n"/>
+      <c r="E55" s="47" t="n"/>
+      <c r="F55" s="48" t="n"/>
       <c r="G55" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -2636,7 +2702,9 @@
       <c r="P55" s="20" t="n">
         <v>0.652855</v>
       </c>
-      <c r="Q55" s="17" t="n"/>
+      <c r="Q55" s="20" t="n">
+        <v>0.652855</v>
+      </c>
       <c r="R55" s="17" t="n"/>
       <c r="S55" s="17" t="n"/>
       <c r="T55" s="17" t="n"/>
@@ -2653,25 +2721,25 @@
           <t>Pek. Pas. Instalasi titik lampu</t>
         </is>
       </c>
-      <c r="D56" s="33" t="n"/>
-      <c r="E56" s="33" t="n"/>
-      <c r="F56" s="34" t="n"/>
+      <c r="D56" s="47" t="n"/>
+      <c r="E56" s="47" t="n"/>
+      <c r="F56" s="48" t="n"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
           <t>titik</t>
         </is>
       </c>
       <c r="H56" s="17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I56" s="18" t="n">
         <v>449902</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>0</v>
+        <v>5398824</v>
       </c>
       <c r="K56" s="17" t="n">
-        <v>0</v>
+        <v>1.505714</v>
       </c>
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="20" t="n">
@@ -2699,9 +2767,9 @@
           <t>Pek. Pasangan lampu TBS/RMI 2 x 8 watt (LED)</t>
         </is>
       </c>
-      <c r="D57" s="33" t="n"/>
-      <c r="E57" s="33" t="n"/>
-      <c r="F57" s="34" t="n"/>
+      <c r="D57" s="47" t="n"/>
+      <c r="E57" s="47" t="n"/>
+      <c r="F57" s="48" t="n"/>
       <c r="G57" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -2724,10 +2792,18 @@
       <c r="N57" s="17" t="n"/>
       <c r="O57" s="17" t="n"/>
       <c r="P57" s="17" t="n"/>
-      <c r="Q57" s="17" t="n"/>
-      <c r="R57" s="17" t="n"/>
-      <c r="S57" s="17" t="n"/>
-      <c r="T57" s="17" t="n"/>
+      <c r="Q57" s="20" t="n">
+        <v>0.55906525</v>
+      </c>
+      <c r="R57" s="20" t="n">
+        <v>0.55906525</v>
+      </c>
+      <c r="S57" s="20" t="n">
+        <v>0.55906525</v>
+      </c>
+      <c r="T57" s="20" t="n">
+        <v>0.55906525</v>
+      </c>
       <c r="U57" s="17" t="n"/>
       <c r="V57" s="11" t="n"/>
       <c r="W57" s="19" t="n"/>
@@ -2741,9 +2817,9 @@
           <t xml:space="preserve">Pek. Pas. Saklar ganda </t>
         </is>
       </c>
-      <c r="D58" s="33" t="n"/>
-      <c r="E58" s="33" t="n"/>
-      <c r="F58" s="34" t="n"/>
+      <c r="D58" s="47" t="n"/>
+      <c r="E58" s="47" t="n"/>
+      <c r="F58" s="48" t="n"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -2766,10 +2842,18 @@
       <c r="N58" s="17" t="n"/>
       <c r="O58" s="17" t="n"/>
       <c r="P58" s="17" t="n"/>
-      <c r="Q58" s="17" t="n"/>
-      <c r="R58" s="17" t="n"/>
-      <c r="S58" s="17" t="n"/>
-      <c r="T58" s="17" t="n"/>
+      <c r="Q58" s="20" t="n">
+        <v>0.013324</v>
+      </c>
+      <c r="R58" s="20" t="n">
+        <v>0.013324</v>
+      </c>
+      <c r="S58" s="20" t="n">
+        <v>0.013324</v>
+      </c>
+      <c r="T58" s="20" t="n">
+        <v>0.013324</v>
+      </c>
       <c r="U58" s="17" t="n"/>
       <c r="V58" s="11" t="n"/>
       <c r="W58" s="19" t="n"/>
@@ -2809,9 +2893,9 @@
           <t>GEDUNG KELAS II (LANTAI 2)</t>
         </is>
       </c>
-      <c r="D60" s="33" t="n"/>
-      <c r="E60" s="33" t="n"/>
-      <c r="F60" s="34" t="n"/>
+      <c r="D60" s="47" t="n"/>
+      <c r="E60" s="47" t="n"/>
+      <c r="F60" s="48" t="n"/>
       <c r="G60" s="13" t="n"/>
       <c r="H60" s="13" t="n"/>
       <c r="I60" s="13" t="n"/>
@@ -2839,9 +2923,9 @@
           <t>Pek. Bongkaran plafond</t>
         </is>
       </c>
-      <c r="D61" s="33" t="n"/>
-      <c r="E61" s="33" t="n"/>
-      <c r="F61" s="34" t="n"/>
+      <c r="D61" s="47" t="n"/>
+      <c r="E61" s="47" t="n"/>
+      <c r="F61" s="48" t="n"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -2885,9 +2969,9 @@
           <t>Pek. Pas. Plafond PVC Putih Polos</t>
         </is>
       </c>
-      <c r="D62" s="33" t="n"/>
-      <c r="E62" s="33" t="n"/>
-      <c r="F62" s="34" t="n"/>
+      <c r="D62" s="47" t="n"/>
+      <c r="E62" s="47" t="n"/>
+      <c r="F62" s="48" t="n"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -2914,8 +2998,12 @@
       <c r="P62" s="20" t="n">
         <v>3.41706567</v>
       </c>
-      <c r="Q62" s="17" t="n"/>
-      <c r="R62" s="17" t="n"/>
+      <c r="Q62" s="20" t="n">
+        <v>3.41706567</v>
+      </c>
+      <c r="R62" s="20" t="n">
+        <v>1.70853283</v>
+      </c>
       <c r="S62" s="17" t="n"/>
       <c r="T62" s="17" t="n"/>
       <c r="U62" s="17" t="n"/>
@@ -2931,9 +3019,9 @@
           <t>Pek. List Plafond PVC Putih</t>
         </is>
       </c>
-      <c r="D63" s="33" t="n"/>
-      <c r="E63" s="33" t="n"/>
-      <c r="F63" s="34" t="n"/>
+      <c r="D63" s="47" t="n"/>
+      <c r="E63" s="47" t="n"/>
+      <c r="F63" s="48" t="n"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
           <t>m'</t>
@@ -2960,8 +3048,12 @@
       <c r="P63" s="20" t="n">
         <v>0.12746625</v>
       </c>
-      <c r="Q63" s="17" t="n"/>
-      <c r="R63" s="17" t="n"/>
+      <c r="Q63" s="20" t="n">
+        <v>0.12746625</v>
+      </c>
+      <c r="R63" s="20" t="n">
+        <v>0.12746625</v>
+      </c>
       <c r="S63" s="17" t="n"/>
       <c r="T63" s="17" t="n"/>
       <c r="U63" s="17" t="n"/>
@@ -2977,9 +3069,9 @@
           <t>Pek. Pengecatan Plafond</t>
         </is>
       </c>
-      <c r="D64" s="33" t="n"/>
-      <c r="E64" s="33" t="n"/>
-      <c r="F64" s="34" t="n"/>
+      <c r="D64" s="47" t="n"/>
+      <c r="E64" s="47" t="n"/>
+      <c r="F64" s="48" t="n"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -3008,7 +3100,9 @@
       <c r="P64" s="20" t="n">
         <v>0.5159792</v>
       </c>
-      <c r="Q64" s="17" t="n"/>
+      <c r="Q64" s="20" t="n">
+        <v>0.1300014</v>
+      </c>
       <c r="R64" s="17" t="n"/>
       <c r="S64" s="17" t="n"/>
       <c r="T64" s="17" t="n"/>
@@ -3025,25 +3119,25 @@
           <t>Pek. Pas. Instalasi titik lampu</t>
         </is>
       </c>
-      <c r="D65" s="33" t="n"/>
-      <c r="E65" s="33" t="n"/>
-      <c r="F65" s="34" t="n"/>
+      <c r="D65" s="47" t="n"/>
+      <c r="E65" s="47" t="n"/>
+      <c r="F65" s="48" t="n"/>
       <c r="G65" s="7" t="inlineStr">
         <is>
           <t>titik</t>
         </is>
       </c>
       <c r="H65" s="17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I65" s="18" t="n">
         <v>449902</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>0</v>
+        <v>3599216</v>
       </c>
       <c r="K65" s="17" t="n">
-        <v>0</v>
+        <v>1.003809</v>
       </c>
       <c r="L65" s="11" t="n"/>
       <c r="M65" s="20" t="n">
@@ -3071,9 +3165,9 @@
           <t>Pek. Pasangan lampu TBS/RMI 2 x 8 watt (LED)</t>
         </is>
       </c>
-      <c r="D66" s="33" t="n"/>
-      <c r="E66" s="33" t="n"/>
-      <c r="F66" s="34" t="n"/>
+      <c r="D66" s="47" t="n"/>
+      <c r="E66" s="47" t="n"/>
+      <c r="F66" s="48" t="n"/>
       <c r="G66" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -3096,10 +3190,18 @@
       <c r="N66" s="17" t="n"/>
       <c r="O66" s="17" t="n"/>
       <c r="P66" s="17" t="n"/>
-      <c r="Q66" s="17" t="n"/>
-      <c r="R66" s="17" t="n"/>
-      <c r="S66" s="17" t="n"/>
-      <c r="T66" s="17" t="n"/>
+      <c r="Q66" s="20" t="n">
+        <v>0.37271025</v>
+      </c>
+      <c r="R66" s="20" t="n">
+        <v>0.37271025</v>
+      </c>
+      <c r="S66" s="20" t="n">
+        <v>0.37271025</v>
+      </c>
+      <c r="T66" s="20" t="n">
+        <v>0.37271025</v>
+      </c>
       <c r="U66" s="17" t="n"/>
       <c r="V66" s="11" t="n"/>
       <c r="W66" s="19" t="n"/>
@@ -3113,9 +3215,9 @@
           <t xml:space="preserve">Pek. Pas. Saklar ganda </t>
         </is>
       </c>
-      <c r="D67" s="33" t="n"/>
-      <c r="E67" s="33" t="n"/>
-      <c r="F67" s="34" t="n"/>
+      <c r="D67" s="47" t="n"/>
+      <c r="E67" s="47" t="n"/>
+      <c r="F67" s="48" t="n"/>
       <c r="G67" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -3138,10 +3240,18 @@
       <c r="N67" s="17" t="n"/>
       <c r="O67" s="17" t="n"/>
       <c r="P67" s="17" t="n"/>
-      <c r="Q67" s="17" t="n"/>
-      <c r="R67" s="17" t="n"/>
-      <c r="S67" s="17" t="n"/>
-      <c r="T67" s="17" t="n"/>
+      <c r="Q67" s="20" t="n">
+        <v>0.00888275</v>
+      </c>
+      <c r="R67" s="20" t="n">
+        <v>0.00888275</v>
+      </c>
+      <c r="S67" s="20" t="n">
+        <v>0.00888275</v>
+      </c>
+      <c r="T67" s="20" t="n">
+        <v>0.00888275</v>
+      </c>
       <c r="U67" s="17" t="n"/>
       <c r="V67" s="11" t="n"/>
       <c r="W67" s="19" t="n"/>
@@ -3181,9 +3291,9 @@
           <t xml:space="preserve">GEDUNG KELAS III </t>
         </is>
       </c>
-      <c r="D69" s="33" t="n"/>
-      <c r="E69" s="33" t="n"/>
-      <c r="F69" s="34" t="n"/>
+      <c r="D69" s="47" t="n"/>
+      <c r="E69" s="47" t="n"/>
+      <c r="F69" s="48" t="n"/>
       <c r="G69" s="13" t="n"/>
       <c r="H69" s="13" t="n"/>
       <c r="I69" s="13" t="n"/>
@@ -3213,9 +3323,9 @@
           <t>Lantai 1</t>
         </is>
       </c>
-      <c r="D70" s="33" t="n"/>
-      <c r="E70" s="33" t="n"/>
-      <c r="F70" s="34" t="n"/>
+      <c r="D70" s="47" t="n"/>
+      <c r="E70" s="47" t="n"/>
+      <c r="F70" s="48" t="n"/>
       <c r="G70" s="13" t="n"/>
       <c r="H70" s="13" t="n"/>
       <c r="I70" s="13" t="n"/>
@@ -3243,9 +3353,9 @@
           <t>Pek. Bongkaran plafond</t>
         </is>
       </c>
-      <c r="D71" s="33" t="n"/>
-      <c r="E71" s="33" t="n"/>
-      <c r="F71" s="34" t="n"/>
+      <c r="D71" s="47" t="n"/>
+      <c r="E71" s="47" t="n"/>
+      <c r="F71" s="48" t="n"/>
       <c r="G71" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -3271,7 +3381,9 @@
       <c r="Q71" s="17" t="n"/>
       <c r="R71" s="17" t="n"/>
       <c r="S71" s="17" t="n"/>
-      <c r="T71" s="17" t="n"/>
+      <c r="T71" s="20" t="n">
+        <v>0.0077</v>
+      </c>
       <c r="U71" s="17" t="n"/>
       <c r="V71" s="11" t="n"/>
       <c r="W71" s="19" t="n"/>
@@ -3285,9 +3397,9 @@
           <t>Pek. Pas. Plafond PVC Putih Polos</t>
         </is>
       </c>
-      <c r="D72" s="33" t="n"/>
-      <c r="E72" s="33" t="n"/>
-      <c r="F72" s="34" t="n"/>
+      <c r="D72" s="47" t="n"/>
+      <c r="E72" s="47" t="n"/>
+      <c r="F72" s="48" t="n"/>
       <c r="G72" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -3313,8 +3425,12 @@
       <c r="Q72" s="17" t="n"/>
       <c r="R72" s="17" t="n"/>
       <c r="S72" s="17" t="n"/>
-      <c r="T72" s="17" t="n"/>
-      <c r="U72" s="17" t="n"/>
+      <c r="T72" s="20" t="n">
+        <v>0.238524</v>
+      </c>
+      <c r="U72" s="20" t="n">
+        <v>0.119262</v>
+      </c>
       <c r="V72" s="11" t="n"/>
       <c r="W72" s="19" t="n"/>
     </row>
@@ -3327,9 +3443,9 @@
           <t>Pek. List Plafond PVC Putih</t>
         </is>
       </c>
-      <c r="D73" s="33" t="n"/>
-      <c r="E73" s="33" t="n"/>
-      <c r="F73" s="34" t="n"/>
+      <c r="D73" s="47" t="n"/>
+      <c r="E73" s="47" t="n"/>
+      <c r="F73" s="48" t="n"/>
       <c r="G73" s="7" t="inlineStr">
         <is>
           <t>m'</t>
@@ -3355,8 +3471,12 @@
       <c r="Q73" s="17" t="n"/>
       <c r="R73" s="17" t="n"/>
       <c r="S73" s="17" t="n"/>
-      <c r="T73" s="17" t="n"/>
-      <c r="U73" s="17" t="n"/>
+      <c r="T73" s="20" t="n">
+        <v>0.06340867</v>
+      </c>
+      <c r="U73" s="20" t="n">
+        <v>0.03170433</v>
+      </c>
       <c r="V73" s="11" t="n"/>
       <c r="W73" s="19" t="n"/>
     </row>
@@ -3369,9 +3489,9 @@
           <t>Pek. Pengecatan Plafond</t>
         </is>
       </c>
-      <c r="D74" s="33" t="n"/>
-      <c r="E74" s="33" t="n"/>
-      <c r="F74" s="34" t="n"/>
+      <c r="D74" s="47" t="n"/>
+      <c r="E74" s="47" t="n"/>
+      <c r="F74" s="48" t="n"/>
       <c r="G74" s="7" t="inlineStr">
         <is>
           <t>titik</t>
@@ -3397,8 +3517,12 @@
       <c r="Q74" s="17" t="n"/>
       <c r="R74" s="17" t="n"/>
       <c r="S74" s="17" t="n"/>
-      <c r="T74" s="17" t="n"/>
-      <c r="U74" s="17" t="n"/>
+      <c r="T74" s="20" t="n">
+        <v>0.022808</v>
+      </c>
+      <c r="U74" s="20" t="n">
+        <v>0.011404</v>
+      </c>
       <c r="V74" s="11" t="n"/>
       <c r="W74" s="19" t="n"/>
     </row>
@@ -3411,9 +3535,9 @@
           <t>Pek. Pas. Instalasi titik lampu</t>
         </is>
       </c>
-      <c r="D75" s="33" t="n"/>
-      <c r="E75" s="33" t="n"/>
-      <c r="F75" s="34" t="n"/>
+      <c r="D75" s="47" t="n"/>
+      <c r="E75" s="47" t="n"/>
+      <c r="F75" s="48" t="n"/>
       <c r="G75" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -3439,8 +3563,12 @@
       <c r="Q75" s="17" t="n"/>
       <c r="R75" s="17" t="n"/>
       <c r="S75" s="17" t="n"/>
-      <c r="T75" s="17" t="n"/>
-      <c r="U75" s="17" t="n"/>
+      <c r="T75" s="20" t="n">
+        <v>0.16730133</v>
+      </c>
+      <c r="U75" s="20" t="n">
+        <v>0.08365067</v>
+      </c>
       <c r="V75" s="11" t="n"/>
       <c r="W75" s="19" t="n"/>
     </row>
@@ -3453,9 +3581,9 @@
           <t>Pek. Pas. Saklar single</t>
         </is>
       </c>
-      <c r="D76" s="33" t="n"/>
-      <c r="E76" s="33" t="n"/>
-      <c r="F76" s="34" t="n"/>
+      <c r="D76" s="47" t="n"/>
+      <c r="E76" s="47" t="n"/>
+      <c r="F76" s="48" t="n"/>
       <c r="G76" s="7" t="inlineStr">
         <is>
           <t>bh</t>
@@ -3481,8 +3609,12 @@
       <c r="Q76" s="17" t="n"/>
       <c r="R76" s="17" t="n"/>
       <c r="S76" s="17" t="n"/>
-      <c r="T76" s="17" t="n"/>
-      <c r="U76" s="17" t="n"/>
+      <c r="T76" s="20" t="n">
+        <v>0.02368733</v>
+      </c>
+      <c r="U76" s="20" t="n">
+        <v>0.01184367</v>
+      </c>
       <c r="V76" s="11" t="n"/>
       <c r="W76" s="19" t="n"/>
     </row>
@@ -3521,9 +3653,9 @@
           <t>Lantai 2</t>
         </is>
       </c>
-      <c r="D78" s="33" t="n"/>
-      <c r="E78" s="33" t="n"/>
-      <c r="F78" s="34" t="n"/>
+      <c r="D78" s="47" t="n"/>
+      <c r="E78" s="47" t="n"/>
+      <c r="F78" s="48" t="n"/>
       <c r="G78" s="13" t="n"/>
       <c r="H78" s="13" t="n"/>
       <c r="I78" s="13" t="n"/>
@@ -3551,9 +3683,9 @@
           <t>Pek. Plesteran Pada Pelat Lantai Keropos</t>
         </is>
       </c>
-      <c r="D79" s="33" t="n"/>
-      <c r="E79" s="33" t="n"/>
-      <c r="F79" s="34" t="n"/>
+      <c r="D79" s="47" t="n"/>
+      <c r="E79" s="47" t="n"/>
+      <c r="F79" s="48" t="n"/>
       <c r="G79" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -3595,25 +3727,25 @@
           <t>Pek. Bongkaran plafond</t>
         </is>
       </c>
-      <c r="D80" s="33" t="n"/>
-      <c r="E80" s="33" t="n"/>
-      <c r="F80" s="34" t="n"/>
+      <c r="D80" s="47" t="n"/>
+      <c r="E80" s="47" t="n"/>
+      <c r="F80" s="48" t="n"/>
       <c r="G80" s="7" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
       <c r="H80" s="17" t="n">
-        <v>67.87462499999999</v>
+        <v>135.74925</v>
       </c>
       <c r="I80" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>373310.4374999999</v>
+        <v>746620.8749999999</v>
       </c>
       <c r="K80" s="17" t="n">
-        <v>0.104115</v>
+        <v>0.20823</v>
       </c>
       <c r="L80" s="11" t="n"/>
       <c r="M80" s="20" t="n">
@@ -3639,25 +3771,25 @@
           <t>Pek. Pas. Plafond PVC Putih Polos</t>
         </is>
       </c>
-      <c r="D81" s="33" t="n"/>
-      <c r="E81" s="33" t="n"/>
-      <c r="F81" s="34" t="n"/>
+      <c r="D81" s="47" t="n"/>
+      <c r="E81" s="47" t="n"/>
+      <c r="F81" s="48" t="n"/>
       <c r="G81" s="7" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
       <c r="H81" s="17" t="n">
-        <v>67.87462499999999</v>
+        <v>135.74925</v>
       </c>
       <c r="I81" s="18" t="n">
         <v>255550</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>17345360.41875</v>
+        <v>34690720.8375</v>
       </c>
       <c r="K81" s="17" t="n">
-        <v>4.837562</v>
+        <v>9.675122999999999</v>
       </c>
       <c r="L81" s="11" t="n"/>
       <c r="M81" s="17" t="n"/>
@@ -3687,25 +3819,25 @@
           <t>Pek. List Plafond PVC Putih</t>
         </is>
       </c>
-      <c r="D82" s="33" t="n"/>
-      <c r="E82" s="33" t="n"/>
-      <c r="F82" s="34" t="n"/>
+      <c r="D82" s="47" t="n"/>
+      <c r="E82" s="47" t="n"/>
+      <c r="F82" s="48" t="n"/>
       <c r="G82" s="7" t="inlineStr">
         <is>
           <t>m'</t>
         </is>
       </c>
       <c r="H82" s="17" t="n">
-        <v>33.02</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="I82" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>886686.0600000001</v>
+        <v>1773372.12</v>
       </c>
       <c r="K82" s="17" t="n">
-        <v>0.247294</v>
+        <v>0.494587</v>
       </c>
       <c r="L82" s="11" t="n"/>
       <c r="M82" s="17" t="n"/>
@@ -3733,9 +3865,9 @@
           <t>Pek. Pengecatan Plafond</t>
         </is>
       </c>
-      <c r="D83" s="33" t="n"/>
-      <c r="E83" s="33" t="n"/>
-      <c r="F83" s="34" t="n"/>
+      <c r="D83" s="47" t="n"/>
+      <c r="E83" s="47" t="n"/>
+      <c r="F83" s="48" t="n"/>
       <c r="G83" s="7" t="inlineStr">
         <is>
           <t>m2</t>
@@ -3758,9 +3890,15 @@
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n"/>
       <c r="P83" s="17" t="n"/>
-      <c r="Q83" s="17" t="n"/>
-      <c r="R83" s="17" t="n"/>
-      <c r="S83" s="17" t="n"/>
+      <c r="Q83" s="20" t="n">
+        <v>0.1845066</v>
+      </c>
+      <c r="R83" s="20" t="n">
+        <v>0.34594988</v>
+      </c>
+      <c r="S83" s="20" t="n">
+        <v>2.23714252</v>
+      </c>
       <c r="T83" s="17" t="n"/>
       <c r="U83" s="17" t="n"/>
       <c r="V83" s="11" t="n"/>
@@ -3775,25 +3913,25 @@
           <t>Pek. Pas. Instalasi titik lampu</t>
         </is>
       </c>
-      <c r="D84" s="33" t="n"/>
-      <c r="E84" s="33" t="n"/>
-      <c r="F84" s="34" t="n"/>
+      <c r="D84" s="47" t="n"/>
+      <c r="E84" s="47" t="n"/>
+      <c r="F84" s="48" t="n"/>
       <c r="G84" s="7" t="inlineStr">
         <is>
           <t>titik</t>
         </is>
       </c>
       <c r="H84" s="17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I84" s="18" t="n">
         <v>449902</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>0</v>
+        <v>3599216</v>
       </c>
       <c r="K84" s="17" t="n">
-        <v>0</v>
+        <v>1.003809</v>
       </c>
       <c r="L84" s="11" t="n"/>
       <c r="M84" s="17" t="n"/>
@@ -3821,25 +3959,25 @@
           <t>Pek. Pasangan lampu TBS/RMI 2 x 8 watt (LED)</t>
         </is>
       </c>
-      <c r="D85" s="33" t="n"/>
-      <c r="E85" s="33" t="n"/>
-      <c r="F85" s="34" t="n"/>
+      <c r="D85" s="47" t="n"/>
+      <c r="E85" s="47" t="n"/>
+      <c r="F85" s="48" t="n"/>
       <c r="G85" s="7" t="inlineStr">
         <is>
           <t>bh</t>
         </is>
       </c>
       <c r="H85" s="17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I85" s="18" t="n">
         <v>668187</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>2672748</v>
+        <v>5345496</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>0.74542</v>
+        <v>1.490841</v>
       </c>
       <c r="L85" s="11" t="n"/>
       <c r="M85" s="17" t="n"/>
@@ -3849,8 +3987,12 @@
       <c r="Q85" s="17" t="n"/>
       <c r="R85" s="17" t="n"/>
       <c r="S85" s="17" t="n"/>
-      <c r="T85" s="17" t="n"/>
-      <c r="U85" s="17" t="n"/>
+      <c r="T85" s="20" t="n">
+        <v>0.7454205</v>
+      </c>
+      <c r="U85" s="20" t="n">
+        <v>0.7454205</v>
+      </c>
       <c r="V85" s="11" t="n"/>
       <c r="W85" s="19" t="n"/>
     </row>
@@ -3863,25 +4005,25 @@
           <t xml:space="preserve">Pek. Pas. Saklar ganda </t>
         </is>
       </c>
-      <c r="D86" s="33" t="n"/>
-      <c r="E86" s="33" t="n"/>
-      <c r="F86" s="34" t="n"/>
+      <c r="D86" s="47" t="n"/>
+      <c r="E86" s="47" t="n"/>
+      <c r="F86" s="48" t="n"/>
       <c r="G86" s="7" t="inlineStr">
         <is>
           <t>bh</t>
         </is>
       </c>
       <c r="H86" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86" s="18" t="n">
         <v>63699</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>63699</v>
+        <v>127398</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>0.017765</v>
+        <v>0.035531</v>
       </c>
       <c r="L86" s="11" t="n"/>
       <c r="M86" s="17" t="n"/>
@@ -3891,8 +4033,12 @@
       <c r="Q86" s="17" t="n"/>
       <c r="R86" s="17" t="n"/>
       <c r="S86" s="17" t="n"/>
-      <c r="T86" s="17" t="n"/>
-      <c r="U86" s="17" t="n"/>
+      <c r="T86" s="20" t="n">
+        <v>0.0177655</v>
+      </c>
+      <c r="U86" s="20" t="n">
+        <v>0.0177655</v>
+      </c>
       <c r="V86" s="11" t="n"/>
       <c r="W86" s="19" t="n"/>
     </row>
@@ -3931,9 +4077,9 @@
           <t>GEDUNG KELAS IV (LANTAI 2)</t>
         </is>
       </c>
-      <c r="D88" s="33" t="n"/>
-      <c r="E88" s="33" t="n"/>
-      <c r="F88" s="34" t="n"/>
+      <c r="D88" s="47" t="n"/>
+      <c r="E88" s="47" t="n"/>
+      <c r="F88" s="48" t="n"/>
       <c r="G88" s="13" t="n"/>
       <c r="H88" s="13" t="n"/>
       <c r="I88" s="13" t="n"/>
@@ -3963,9 +4109,9 @@
           <t>Lantai 1</t>
         </is>
       </c>
-      <c r="D89" s="33" t="n"/>
-      <c r="E89" s="33" t="n"/>
-      <c r="F89" s="34" t="n"/>
+      <c r="D89" s="47" t="n"/>
+      <c r="E89" s="47" t="n"/>
+      <c r="F89" s="48" t="n"/>
       <c r="G89" s="13" t="n"/>
       <c r="H89" s="13" t="n"/>
       <c r="I89" s="13" t="n"/>
@@ -3993,25 +4139,25 @@
           <t>Pek. Bongkaran plafond</t>
         </is>
       </c>
-      <c r="D90" s="33" t="n"/>
-      <c r="E90" s="33" t="n"/>
-      <c r="F90" s="34" t="n"/>
+      <c r="D90" s="47" t="n"/>
+      <c r="E90" s="47" t="n"/>
+      <c r="F90" s="48" t="n"/>
       <c r="G90" s="7" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
       <c r="H90" s="17" t="n">
-        <v>572.822</v>
+        <v>414.1776</v>
       </c>
       <c r="I90" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>3150521</v>
+        <v>2277976.8</v>
       </c>
       <c r="K90" s="17" t="n">
-        <v>0.87867</v>
+        <v>0.63532</v>
       </c>
       <c r="L90" s="11" t="n"/>
       <c r="M90" s="17" t="n"/>
@@ -4037,25 +4183,25 @@
           <t>Pek. Pas. Plafond PVC Putih Polos</t>
         </is>
       </c>
-      <c r="D91" s="33" t="n"/>
-      <c r="E91" s="33" t="n"/>
-      <c r="F91" s="34" t="n"/>
+      <c r="D91" s="47" t="n"/>
+      <c r="E91" s="47" t="n"/>
+      <c r="F91" s="48" t="n"/>
       <c r="G91" s="7" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
       <c r="H91" s="17" t="n">
-        <v>297.18</v>
+        <v>240.9876</v>
       </c>
       <c r="I91" s="18" t="n">
         <v>255550</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>75944349</v>
+        <v>61584381.18</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>21.180619</v>
+        <v>17.175673</v>
       </c>
       <c r="L91" s="11" t="n"/>
       <c r="M91" s="17" t="n"/>
@@ -4066,9 +4212,15 @@
       <c r="P91" s="20" t="n">
         <v>5.18136414</v>
       </c>
-      <c r="Q91" s="17" t="n"/>
-      <c r="R91" s="17" t="n"/>
-      <c r="S91" s="17" t="n"/>
+      <c r="Q91" s="20" t="n">
+        <v>4.29391825</v>
+      </c>
+      <c r="R91" s="20" t="n">
+        <v>3.37309328</v>
+      </c>
+      <c r="S91" s="20" t="n">
+        <v>3.37309328</v>
+      </c>
       <c r="T91" s="17" t="n"/>
       <c r="U91" s="17" t="n"/>
       <c r="V91" s="11" t="n"/>
@@ -4083,25 +4235,25 @@
           <t>Pek. Pas. Plafond PVC Motif Kayu</t>
         </is>
       </c>
-      <c r="D92" s="33" t="n"/>
-      <c r="E92" s="33" t="n"/>
-      <c r="F92" s="34" t="n"/>
+      <c r="D92" s="47" t="n"/>
+      <c r="E92" s="47" t="n"/>
+      <c r="F92" s="48" t="n"/>
       <c r="G92" s="7" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
       <c r="H92" s="17" t="n">
-        <v>275.642</v>
+        <v>173.19</v>
       </c>
       <c r="I92" s="18" t="n">
         <v>277206</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>76409616.252</v>
+        <v>48009307.14</v>
       </c>
       <c r="K92" s="17" t="n">
-        <v>21.31038</v>
+        <v>13.389631</v>
       </c>
       <c r="L92" s="11" t="n"/>
       <c r="M92" s="17" t="n"/>
@@ -4112,9 +4264,15 @@
       <c r="P92" s="20" t="n">
         <v>9.231605220000001</v>
       </c>
-      <c r="Q92" s="17" t="n"/>
-      <c r="R92" s="17" t="n"/>
-      <c r="S92" s="17" t="n"/>
+      <c r="Q92" s="20" t="n">
+        <v>3.34740775</v>
+      </c>
+      <c r="R92" s="20" t="n">
+        <v>0.03337482</v>
+      </c>
+      <c r="S92" s="20" t="n">
+        <v>0.03337482</v>
+      </c>
       <c r="T92" s="17" t="n"/>
       <c r="U92" s="17" t="n"/>
       <c r="V92" s="11" t="n"/>
@@ -4129,25 +4287,25 @@
           <t>Pek. List Plafond PVC Putih</t>
         </is>
       </c>
-      <c r="D93" s="33" t="n"/>
-      <c r="E93" s="33" t="n"/>
-      <c r="F93" s="34" t="n"/>
+      <c r="D93" s="47" t="n"/>
+      <c r="E93" s="47" t="n"/>
+      <c r="F93" s="48" t="n"/>
       <c r="G93" s="7" t="inlineStr">
         <is>
           <t>m'</t>
         </is>
       </c>
       <c r="H93" s="17" t="n">
-        <v>154.2</v>
+        <v>124.2</v>
       </c>
       <c r="I93" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>4140732.6</v>
+        <v>3335142.6</v>
       </c>
       <c r="K93" s="17" t="n">
-        <v>1.154836</v>
+        <v>0.93016</v>
       </c>
       <c r="L93" s="11" t="n"/>
       <c r="M93" s="17" t="n"/>
@@ -4158,9 +4316,15 @@
       <c r="P93" s="20" t="n">
         <v>0.31005333</v>
       </c>
-      <c r="Q93" s="17" t="n"/>
-      <c r="R93" s="17" t="n"/>
-      <c r="S93" s="17" t="n"/>
+      <c r="Q93" s="20" t="n">
+        <v>0.23254</v>
+      </c>
+      <c r="R93" s="20" t="n">
+        <v>0.11627</v>
+      </c>
+      <c r="S93" s="20" t="n">
+        <v>0.11627</v>
+      </c>
       <c r="T93" s="17" t="n"/>
       <c r="U93" s="17" t="n"/>
       <c r="V93" s="11" t="n"/>
@@ -4175,25 +4339,25 @@
           <t>Pek. List Plafond PVC Coklat</t>
         </is>
       </c>
-      <c r="D94" s="33" t="n"/>
-      <c r="E94" s="33" t="n"/>
-      <c r="F94" s="34" t="n"/>
+      <c r="D94" s="47" t="n"/>
+      <c r="E94" s="47" t="n"/>
+      <c r="F94" s="48" t="n"/>
       <c r="G94" s="7" t="inlineStr">
         <is>
           <t>m'</t>
         </is>
       </c>
       <c r="H94" s="17" t="n">
-        <v>267.6554554</v>
+        <v>213.58</v>
       </c>
       <c r="I94" s="18" t="n">
         <v>26853</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>7187351.9438562</v>
+        <v>5735263.74</v>
       </c>
       <c r="K94" s="17" t="n">
-        <v>2.004528</v>
+        <v>1.599545</v>
       </c>
       <c r="L94" s="11" t="n"/>
       <c r="M94" s="17" t="n"/>
@@ -4204,9 +4368,15 @@
       <c r="P94" s="20" t="n">
         <v>0.39988625</v>
       </c>
-      <c r="Q94" s="17" t="n"/>
-      <c r="R94" s="17" t="n"/>
-      <c r="S94" s="17" t="n"/>
+      <c r="Q94" s="20" t="n">
+        <v>0.39988625</v>
+      </c>
+      <c r="R94" s="20" t="n">
+        <v>0.19994313</v>
+      </c>
+      <c r="S94" s="20" t="n">
+        <v>0.19994313</v>
+      </c>
       <c r="T94" s="17" t="n"/>
       <c r="U94" s="17" t="n"/>
       <c r="V94" s="11" t="n"/>
@@ -4221,25 +4391,25 @@
           <t>Pek. Pas. Instalasi titik lampu</t>
         </is>
       </c>
-      <c r="D95" s="33" t="n"/>
-      <c r="E95" s="33" t="n"/>
-      <c r="F95" s="34" t="n"/>
+      <c r="D95" s="47" t="n"/>
+      <c r="E95" s="47" t="n"/>
+      <c r="F95" s="48" t="n"/>
       <c r="G95" s="7" t="inlineStr">
         <is>
           <t>titik</t>
         </is>
       </c>
       <c r="H95" s="17" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I95" s="18" t="n">
         <v>449902</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>6298628</v>
+        <v>17546178</v>
       </c>
       <c r="K95" s="17" t="n">
-        <v>1.756666</v>
+        <v>4.893569</v>
       </c>
       <c r="L95" s="11" t="n"/>
       <c r="M95" s="17" t="n"/>
@@ -4269,25 +4439,25 @@
           <t>Pek. Pas. Lampu 10 watt + downlight</t>
         </is>
       </c>
-      <c r="D96" s="33" t="n"/>
-      <c r="E96" s="33" t="n"/>
-      <c r="F96" s="34" t="n"/>
+      <c r="D96" s="47" t="n"/>
+      <c r="E96" s="47" t="n"/>
+      <c r="F96" s="48" t="n"/>
       <c r="G96" s="7" t="inlineStr">
         <is>
           <t>bh</t>
         </is>
       </c>
       <c r="H96" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I96" s="18" t="n">
         <v>244459</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>3422426</v>
+        <v>3666885</v>
       </c>
       <c r="K96" s="17" t="n">
-        <v>0.954503</v>
+        <v>1.022682</v>
       </c>
       <c r="L96" s="11" t="n"/>
       <c r="M96" s="17" t="n"/>
@@ -4296,8 +4466,12 @@
       <c r="P96" s="17" t="n"/>
       <c r="Q96" s="17" t="n"/>
       <c r="R96" s="17" t="n"/>
-      <c r="S96" s="17" t="n"/>
-      <c r="T96" s="17" t="n"/>
+      <c r="S96" s="20" t="n">
+        <v>0.6817879999999999</v>
+      </c>
+      <c r="T96" s="20" t="n">
+        <v>0.340894</v>
+      </c>
       <c r="U96" s="17" t="n"/>
       <c r="V96" s="11" t="n"/>
       <c r="W96" s="19" t="n"/>
@@ -4311,25 +4485,25 @@
           <t>Pek. Pasangan lampu TBS/RMI 2 x 8 watt (LED)</t>
         </is>
       </c>
-      <c r="D97" s="33" t="n"/>
-      <c r="E97" s="33" t="n"/>
-      <c r="F97" s="34" t="n"/>
+      <c r="D97" s="47" t="n"/>
+      <c r="E97" s="47" t="n"/>
+      <c r="F97" s="48" t="n"/>
       <c r="G97" s="7" t="inlineStr">
         <is>
           <t>bh</t>
         </is>
       </c>
       <c r="H97" s="17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I97" s="18" t="n">
         <v>668187</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>13363740</v>
+        <v>16036488</v>
       </c>
       <c r="K97" s="17" t="n">
-        <v>3.727101</v>
+        <v>4.472522</v>
       </c>
       <c r="L97" s="11" t="n"/>
       <c r="M97" s="17" t="n"/>
@@ -4338,8 +4512,12 @@
       <c r="P97" s="17" t="n"/>
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="17" t="n"/>
-      <c r="S97" s="17" t="n"/>
-      <c r="T97" s="17" t="n"/>
+      <c r="S97" s="20" t="n">
+        <v>2.98168133</v>
+      </c>
+      <c r="T97" s="20" t="n">
+        <v>1.49084067</v>
+      </c>
       <c r="U97" s="17" t="n"/>
       <c r="V97" s="11" t="n"/>
       <c r="W97" s="19" t="n"/>
@@ -4353,25 +4531,25 @@
           <t xml:space="preserve">Pek. Pas. Saklar ganda </t>
         </is>
       </c>
-      <c r="D98" s="33" t="n"/>
-      <c r="E98" s="33" t="n"/>
-      <c r="F98" s="34" t="n"/>
+      <c r="D98" s="47" t="n"/>
+      <c r="E98" s="47" t="n"/>
+      <c r="F98" s="48" t="n"/>
       <c r="G98" s="7" t="inlineStr">
         <is>
           <t>bh</t>
         </is>
       </c>
       <c r="H98" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I98" s="18" t="n">
         <v>63699</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>382194</v>
+        <v>254796</v>
       </c>
       <c r="K98" s="17" t="n">
-        <v>0.106593</v>
+        <v>0.071062</v>
       </c>
       <c r="L98" s="11" t="n"/>
       <c r="M98" s="17" t="n"/>
@@ -4380,8 +4558,12 @@
       <c r="P98" s="17" t="n"/>
       <c r="Q98" s="17" t="n"/>
       <c r="R98" s="17" t="n"/>
-      <c r="S98" s="17" t="n"/>
-      <c r="T98" s="17" t="n"/>
+      <c r="S98" s="20" t="n">
+        <v>0.04737467</v>
+      </c>
+      <c r="T98" s="20" t="n">
+        <v>0.02368733</v>
+      </c>
       <c r="U98" s="17" t="n"/>
       <c r="V98" s="11" t="n"/>
       <c r="W98" s="19" t="n"/>
@@ -4395,25 +4577,25 @@
           <t>Pek. Pas. Saklar single</t>
         </is>
       </c>
-      <c r="D99" s="33" t="n"/>
-      <c r="E99" s="33" t="n"/>
-      <c r="F99" s="34" t="n"/>
+      <c r="D99" s="47" t="n"/>
+      <c r="E99" s="47" t="n"/>
+      <c r="F99" s="48" t="n"/>
       <c r="G99" s="7" t="inlineStr">
         <is>
           <t>bh</t>
         </is>
       </c>
       <c r="H99" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" s="18" t="n">
         <v>46759</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>46759</v>
+        <v>93518</v>
       </c>
       <c r="K99" s="17" t="n">
-        <v>0.013041</v>
+        <v>0.026082</v>
       </c>
       <c r="L99" s="11" t="n"/>
       <c r="M99" s="17" t="n"/>
@@ -4422,8 +4604,12 @@
       <c r="P99" s="17" t="n"/>
       <c r="Q99" s="17" t="n"/>
       <c r="R99" s="17" t="n"/>
-      <c r="S99" s="17" t="n"/>
-      <c r="T99" s="17" t="n"/>
+      <c r="S99" s="20" t="n">
+        <v>0.017388</v>
+      </c>
+      <c r="T99" s="20" t="n">
+        <v>0.008694</v>
+      </c>
       <c r="U99" s="17" t="n"/>
       <c r="V99" s="11" t="n"/>
       <c r="W99" s="19" t="n"/>
@@ -4482,13 +4668,13 @@
           <t>JUMLAH TOTAL</t>
         </is>
       </c>
-      <c r="C102" s="42" t="n"/>
-      <c r="D102" s="42" t="n"/>
-      <c r="E102" s="42" t="n"/>
-      <c r="F102" s="42" t="n"/>
-      <c r="G102" s="42" t="n"/>
-      <c r="H102" s="42" t="n"/>
-      <c r="I102" s="43" t="n"/>
+      <c r="C102" s="33" t="n"/>
+      <c r="D102" s="33" t="n"/>
+      <c r="E102" s="33" t="n"/>
+      <c r="F102" s="33" t="n"/>
+      <c r="G102" s="33" t="n"/>
+      <c r="H102" s="33" t="n"/>
+      <c r="I102" s="49" t="n"/>
       <c r="J102" s="26">
         <f>SUM(J25:J99)</f>
         <v/>
@@ -4507,13 +4693,13 @@
           <t>PPN 11%</t>
         </is>
       </c>
-      <c r="C103" s="42" t="n"/>
-      <c r="D103" s="42" t="n"/>
-      <c r="E103" s="42" t="n"/>
-      <c r="F103" s="42" t="n"/>
-      <c r="G103" s="42" t="n"/>
-      <c r="H103" s="42" t="n"/>
-      <c r="I103" s="43" t="n"/>
+      <c r="C103" s="33" t="n"/>
+      <c r="D103" s="33" t="n"/>
+      <c r="E103" s="33" t="n"/>
+      <c r="F103" s="33" t="n"/>
+      <c r="G103" s="33" t="n"/>
+      <c r="H103" s="33" t="n"/>
+      <c r="I103" s="49" t="n"/>
       <c r="J103" s="26">
         <f>J102*11%</f>
         <v/>
@@ -4529,13 +4715,13 @@
           <t>JUMLAH TOTAL + PPN</t>
         </is>
       </c>
-      <c r="C104" s="42" t="n"/>
-      <c r="D104" s="42" t="n"/>
-      <c r="E104" s="42" t="n"/>
-      <c r="F104" s="42" t="n"/>
-      <c r="G104" s="42" t="n"/>
-      <c r="H104" s="42" t="n"/>
-      <c r="I104" s="43" t="n"/>
+      <c r="C104" s="33" t="n"/>
+      <c r="D104" s="33" t="n"/>
+      <c r="E104" s="33" t="n"/>
+      <c r="F104" s="33" t="n"/>
+      <c r="G104" s="33" t="n"/>
+      <c r="H104" s="33" t="n"/>
+      <c r="I104" s="49" t="n"/>
       <c r="J104" s="26">
         <f>J102+J103</f>
         <v/>
@@ -4551,13 +4737,13 @@
           <t>DIBULATKAN</t>
         </is>
       </c>
-      <c r="C105" s="42" t="n"/>
-      <c r="D105" s="42" t="n"/>
-      <c r="E105" s="42" t="n"/>
-      <c r="F105" s="42" t="n"/>
-      <c r="G105" s="42" t="n"/>
-      <c r="H105" s="42" t="n"/>
-      <c r="I105" s="43" t="n"/>
+      <c r="C105" s="33" t="n"/>
+      <c r="D105" s="33" t="n"/>
+      <c r="E105" s="33" t="n"/>
+      <c r="F105" s="33" t="n"/>
+      <c r="G105" s="33" t="n"/>
+      <c r="H105" s="33" t="n"/>
+      <c r="I105" s="49" t="n"/>
       <c r="J105" s="26">
         <f>ROUND(J104,-3)</f>
         <v/>
@@ -4582,8 +4768,8 @@
           <t>RENCANA FISIK PEKERJAAN</t>
         </is>
       </c>
-      <c r="C106" s="33" t="n"/>
-      <c r="D106" s="34" t="n"/>
+      <c r="C106" s="47" t="n"/>
+      <c r="D106" s="47" t="n"/>
       <c r="E106" s="32" t="inlineStr">
         <is>
           <t>JUMLAH PER-MINGGU</t>
@@ -4594,98 +4780,80 @@
       <c r="H106" s="33" t="n"/>
       <c r="I106" s="33" t="n"/>
       <c r="J106" s="33" t="n"/>
-      <c r="K106" s="34" t="n"/>
+      <c r="K106" s="33" t="n"/>
       <c r="L106" s="28" t="n"/>
-      <c r="M106" s="35">
-        <f>SUBTOTAL(9,M25:M99)</f>
-        <v/>
-      </c>
-      <c r="N106" s="35">
-        <f>SUBTOTAL(9,N25:N99)</f>
-        <v/>
-      </c>
-      <c r="O106" s="35">
-        <f>SUBTOTAL(9,O25:O99)</f>
-        <v/>
-      </c>
-      <c r="P106" s="35">
-        <f>SUBTOTAL(9,P25:P99)</f>
-        <v/>
-      </c>
-      <c r="Q106" s="35">
-        <f>SUBTOTAL(9,Q25:Q99)</f>
-        <v/>
-      </c>
-      <c r="R106" s="35">
-        <f>SUBTOTAL(9,R25:R99)</f>
-        <v/>
-      </c>
-      <c r="S106" s="35">
-        <f>SUBTOTAL(9,S25:S99)</f>
-        <v/>
-      </c>
-      <c r="T106" s="35">
-        <f>SUBTOTAL(9,T25:T99)</f>
-        <v/>
-      </c>
-      <c r="U106" s="35">
-        <f>SUBTOTAL(9,U25:U99)</f>
-        <v/>
+      <c r="M106" s="34" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="N106" s="34" t="n">
+        <v>6.631</v>
+      </c>
+      <c r="O106" s="34" t="n">
+        <v>16.479</v>
+      </c>
+      <c r="P106" s="34" t="n">
+        <v>29.603</v>
+      </c>
+      <c r="Q106" s="34" t="n">
+        <v>17.791</v>
+      </c>
+      <c r="R106" s="34" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="S106" s="34" t="n">
+        <v>10.811</v>
+      </c>
+      <c r="T106" s="34" t="n">
+        <v>4.274</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>1.19</v>
       </c>
       <c r="V106" s="28" t="n"/>
       <c r="W106" s="29" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="51" t="n"/>
+      <c r="B107" s="44" t="n"/>
       <c r="C107" s="30" t="n"/>
-      <c r="D107" s="37" t="n"/>
-      <c r="E107" s="36" t="inlineStr">
+      <c r="D107" s="30" t="n"/>
+      <c r="E107" s="32" t="inlineStr">
         <is>
           <t>JUMLAH KOMULATIF PER-MINGGU</t>
         </is>
       </c>
-      <c r="F107" s="30" t="n"/>
-      <c r="G107" s="30" t="n"/>
-      <c r="H107" s="30" t="n"/>
-      <c r="I107" s="30" t="n"/>
-      <c r="J107" s="30" t="n"/>
-      <c r="K107" s="37" t="n"/>
+      <c r="F107" s="33" t="n"/>
+      <c r="G107" s="33" t="n"/>
+      <c r="H107" s="33" t="n"/>
+      <c r="I107" s="33" t="n"/>
+      <c r="J107" s="33" t="n"/>
+      <c r="K107" s="33" t="n"/>
       <c r="L107" s="28" t="n"/>
-      <c r="M107" s="35">
-        <f>M106</f>
-        <v/>
-      </c>
-      <c r="N107" s="35">
-        <f>M107+N106</f>
-        <v/>
-      </c>
-      <c r="O107" s="35">
-        <f>N107+O106</f>
-        <v/>
-      </c>
-      <c r="P107" s="35">
-        <f>O107+P106</f>
-        <v/>
-      </c>
-      <c r="Q107" s="35">
-        <f>P107+Q106</f>
-        <v/>
-      </c>
-      <c r="R107" s="35">
-        <f>Q107+R106</f>
-        <v/>
-      </c>
-      <c r="S107" s="35">
-        <f>R107+S106</f>
-        <v/>
-      </c>
-      <c r="T107" s="35">
-        <f>S107+T106</f>
-        <v/>
-      </c>
-      <c r="U107" s="35">
-        <f>T107+U106</f>
-        <v/>
+      <c r="M107" s="34" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="N107" s="34" t="n">
+        <v>8.943</v>
+      </c>
+      <c r="O107" s="34" t="n">
+        <v>25.422</v>
+      </c>
+      <c r="P107" s="34" t="n">
+        <v>55.025</v>
+      </c>
+      <c r="Q107" s="34" t="n">
+        <v>72.816</v>
+      </c>
+      <c r="R107" s="34" t="n">
+        <v>83.726</v>
+      </c>
+      <c r="S107" s="34" t="n">
+        <v>94.53700000000001</v>
+      </c>
+      <c r="T107" s="34" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="U107" s="34" t="n">
+        <v>100</v>
       </c>
       <c r="V107" s="28" t="n"/>
       <c r="W107" s="29" t="n"/>
@@ -4696,9 +4864,9 @@
           <t>REALISASI FISIK PEKERJAAN</t>
         </is>
       </c>
-      <c r="C108" s="33" t="n"/>
-      <c r="D108" s="34" t="n"/>
-      <c r="E108" s="38" t="inlineStr">
+      <c r="C108" s="47" t="n"/>
+      <c r="D108" s="47" t="n"/>
+      <c r="E108" s="35" t="inlineStr">
         <is>
           <t>REALISASI PER-MINGGU</t>
         </is>
@@ -4708,215 +4876,269 @@
       <c r="H108" s="33" t="n"/>
       <c r="I108" s="33" t="n"/>
       <c r="J108" s="33" t="n"/>
-      <c r="K108" s="34" t="n"/>
+      <c r="K108" s="33" t="n"/>
       <c r="L108" s="28" t="n"/>
-      <c r="M108" s="35" t="n"/>
-      <c r="N108" s="35" t="n"/>
-      <c r="O108" s="35" t="n"/>
-      <c r="P108" s="35" t="n"/>
-      <c r="Q108" s="35" t="n"/>
-      <c r="R108" s="35" t="n"/>
-      <c r="S108" s="35" t="n"/>
-      <c r="T108" s="35" t="n"/>
-      <c r="U108" s="35" t="n"/>
+      <c r="M108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="V108" s="28" t="n"/>
       <c r="W108" s="29" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="51" t="n"/>
+      <c r="B109" s="44" t="n"/>
       <c r="C109" s="30" t="n"/>
-      <c r="D109" s="37" t="n"/>
-      <c r="E109" s="39" t="inlineStr">
+      <c r="D109" s="30" t="n"/>
+      <c r="E109" s="35" t="inlineStr">
         <is>
           <t>REALISASI KOMULATIF</t>
         </is>
       </c>
-      <c r="F109" s="30" t="n"/>
-      <c r="G109" s="30" t="n"/>
-      <c r="H109" s="30" t="n"/>
-      <c r="I109" s="30" t="n"/>
-      <c r="J109" s="30" t="n"/>
-      <c r="K109" s="37" t="n"/>
+      <c r="F109" s="33" t="n"/>
+      <c r="G109" s="33" t="n"/>
+      <c r="H109" s="33" t="n"/>
+      <c r="I109" s="33" t="n"/>
+      <c r="J109" s="33" t="n"/>
+      <c r="K109" s="33" t="n"/>
       <c r="L109" s="28" t="n"/>
-      <c r="M109" s="35" t="n"/>
-      <c r="N109" s="35" t="n"/>
-      <c r="O109" s="35" t="n"/>
-      <c r="P109" s="35" t="n"/>
-      <c r="Q109" s="35" t="n"/>
-      <c r="R109" s="35" t="n"/>
-      <c r="S109" s="35" t="n"/>
-      <c r="T109" s="35" t="n"/>
-      <c r="U109" s="35" t="n"/>
+      <c r="M109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="V109" s="28" t="n"/>
       <c r="W109" s="29" t="n"/>
     </row>
     <row r="110">
-      <c r="B110" s="40" t="inlineStr">
+      <c r="B110" s="36" t="inlineStr">
         <is>
           <t>DEVIASI</t>
         </is>
       </c>
-      <c r="C110" s="42" t="n"/>
-      <c r="D110" s="43" t="n"/>
-      <c r="E110" s="41" t="inlineStr">
+      <c r="C110" s="33" t="n"/>
+      <c r="D110" s="33" t="n"/>
+      <c r="E110" s="35" t="inlineStr">
         <is>
           <t>JUMLAH KOMULATIF PER-MINGGU</t>
         </is>
       </c>
-      <c r="F110" s="42" t="n"/>
-      <c r="G110" s="42" t="n"/>
-      <c r="H110" s="42" t="n"/>
-      <c r="I110" s="42" t="n"/>
-      <c r="J110" s="42" t="n"/>
-      <c r="K110" s="43" t="n"/>
-      <c r="L110" s="44" t="n"/>
-      <c r="M110" s="35" t="n"/>
-      <c r="N110" s="35" t="n"/>
-      <c r="O110" s="35" t="n"/>
-      <c r="P110" s="35" t="n"/>
-      <c r="Q110" s="35" t="n"/>
-      <c r="R110" s="35" t="n"/>
-      <c r="S110" s="35" t="n"/>
-      <c r="T110" s="35" t="n"/>
-      <c r="U110" s="35" t="n"/>
-      <c r="V110" s="44" t="n"/>
-      <c r="W110" s="45" t="n"/>
+      <c r="F110" s="33" t="n"/>
+      <c r="G110" s="33" t="n"/>
+      <c r="H110" s="33" t="n"/>
+      <c r="I110" s="33" t="n"/>
+      <c r="J110" s="33" t="n"/>
+      <c r="K110" s="33" t="n"/>
+      <c r="L110" s="37" t="n"/>
+      <c r="M110" s="34" t="n">
+        <v>-2.312</v>
+      </c>
+      <c r="N110" s="34" t="n">
+        <v>-8.943</v>
+      </c>
+      <c r="O110" s="34" t="n">
+        <v>-25.422</v>
+      </c>
+      <c r="P110" s="34" t="n">
+        <v>-55.025</v>
+      </c>
+      <c r="Q110" s="34" t="n">
+        <v>-72.816</v>
+      </c>
+      <c r="R110" s="34" t="n">
+        <v>-83.726</v>
+      </c>
+      <c r="S110" s="34" t="n">
+        <v>-94.53700000000001</v>
+      </c>
+      <c r="T110" s="34" t="n">
+        <v>-98.81</v>
+      </c>
+      <c r="U110" s="34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="V110" s="37" t="n"/>
+      <c r="W110" s="38" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="46" t="n"/>
-      <c r="W111" s="47" t="n"/>
+      <c r="B111" s="39" t="n"/>
+      <c r="W111" s="40" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="46" t="n"/>
-      <c r="W112" s="47" t="n"/>
+      <c r="B112" s="39" t="n"/>
+      <c r="W112" s="40" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="46" t="n"/>
-      <c r="F113" s="48" t="inlineStr">
+      <c r="B113" s="39" t="n"/>
+      <c r="F113" s="41" t="inlineStr">
         <is>
           <t>Menyetujui</t>
         </is>
       </c>
-      <c r="M113" s="48" t="inlineStr">
+      <c r="M113" s="41" t="inlineStr">
         <is>
           <t>Diperiksa Oleh</t>
         </is>
       </c>
-      <c r="U113" s="48" t="inlineStr">
+      <c r="U113" s="41" t="inlineStr">
         <is>
           <t>Badung, 2 Maret 2026</t>
         </is>
       </c>
-      <c r="W113" s="47" t="n"/>
+      <c r="W113" s="40" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="46" t="n"/>
-      <c r="F114" s="48" t="inlineStr">
+      <c r="B114" s="39" t="n"/>
+      <c r="F114" s="41" t="inlineStr">
         <is>
           <t>Pejabat Pembuat Komitmen (PPK)</t>
         </is>
       </c>
-      <c r="M114" s="48" t="inlineStr">
+      <c r="M114" s="41" t="inlineStr">
         <is>
           <t>Konsultan Pengawas</t>
         </is>
       </c>
-      <c r="U114" s="48" t="inlineStr">
+      <c r="U114" s="41" t="inlineStr">
         <is>
           <t>Dibuat Oleh</t>
         </is>
       </c>
-      <c r="W114" s="47" t="n"/>
+      <c r="W114" s="40" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="46" t="n"/>
-      <c r="F115" s="48" t="inlineStr">
+      <c r="B115" s="39" t="n"/>
+      <c r="F115" s="41" t="inlineStr">
         <is>
           <t>Kepala Bidang Pendidikan Sekolah Menengah Pertama</t>
         </is>
       </c>
-      <c r="M115" s="48" t="inlineStr">
+      <c r="M115" s="41" t="inlineStr">
         <is>
           <t>CV. GANESHA TEKNIKA</t>
         </is>
       </c>
-      <c r="U115" s="48" t="inlineStr">
+      <c r="U115" s="41" t="inlineStr">
         <is>
           <t>Kontraktor Pelaksana</t>
         </is>
       </c>
-      <c r="W115" s="47" t="n"/>
+      <c r="W115" s="40" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="46" t="n"/>
-      <c r="F116" s="48" t="inlineStr">
+      <c r="B116" s="39" t="n"/>
+      <c r="F116" s="41" t="inlineStr">
         <is>
           <t>Dinas Pendidikan, Kepemudaan, dan Olahraga Kabupaten Badung</t>
         </is>
       </c>
-      <c r="U116" s="48" t="inlineStr">
+      <c r="U116" s="41" t="inlineStr">
         <is>
           <t>CV. BATU KARANG</t>
         </is>
       </c>
-      <c r="W116" s="47" t="n"/>
+      <c r="W116" s="40" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="46" t="n"/>
-      <c r="W117" s="47" t="n"/>
+      <c r="B117" s="39" t="n"/>
+      <c r="W117" s="40" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="46" t="n"/>
-      <c r="W118" s="47" t="n"/>
+      <c r="B118" s="39" t="n"/>
+      <c r="W118" s="40" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="46" t="n"/>
-      <c r="W119" s="47" t="n"/>
+      <c r="B119" s="39" t="n"/>
+      <c r="W119" s="40" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="46" t="n"/>
-      <c r="W120" s="47" t="n"/>
+      <c r="B120" s="39" t="n"/>
+      <c r="W120" s="40" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="46" t="n"/>
-      <c r="F121" s="49" t="inlineStr">
+      <c r="B121" s="39" t="n"/>
+      <c r="F121" s="42" t="inlineStr">
         <is>
           <t>I Nyoman Agus Satwika Ariada, ST.</t>
         </is>
       </c>
-      <c r="M121" s="49" t="inlineStr">
+      <c r="M121" s="42" t="inlineStr">
         <is>
           <t>Ir. Ni Putu Nurzely Astuti, ST.,M.Si</t>
         </is>
       </c>
-      <c r="U121" s="49" t="inlineStr">
+      <c r="U121" s="42" t="inlineStr">
         <is>
           <t>I Made Widihasa Karang</t>
         </is>
       </c>
-      <c r="W121" s="47" t="n"/>
+      <c r="W121" s="40" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="46" t="n"/>
-      <c r="F122" s="50" t="inlineStr">
+      <c r="B122" s="39" t="n"/>
+      <c r="F122" s="43" t="inlineStr">
         <is>
           <t>NIP : 19630530 199703 1 003</t>
         </is>
       </c>
-      <c r="M122" s="50" t="inlineStr">
+      <c r="M122" s="43" t="inlineStr">
         <is>
           <t>Direktur</t>
         </is>
       </c>
-      <c r="U122" s="50" t="inlineStr">
+      <c r="U122" s="43" t="inlineStr">
         <is>
           <t>Direktur</t>
         </is>
       </c>
-      <c r="W122" s="47" t="n"/>
+      <c r="W122" s="40" t="n"/>
     </row>
     <row r="123">
-      <c r="B123" s="51" t="n"/>
+      <c r="B123" s="44" t="n"/>
       <c r="C123" s="30" t="n"/>
       <c r="D123" s="30" t="n"/>
       <c r="E123" s="30" t="n"/>
@@ -4937,7 +5159,7 @@
       <c r="T123" s="30" t="n"/>
       <c r="U123" s="30" t="n"/>
       <c r="V123" s="30" t="n"/>
-      <c r="W123" s="37" t="n"/>
+      <c r="W123" s="45" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="88">
@@ -5071,11 +5293,11 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n">
+      <c r="B2" s="46" t="n">
         <v>2.312</v>
       </c>
-      <c r="C2" s="52" t="n">
-        <v>7.252</v>
+      <c r="C2" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
@@ -5087,11 +5309,11 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n">
+      <c r="B3" s="46" t="n">
         <v>8.943</v>
       </c>
-      <c r="C3" s="52" t="n">
-        <v>10.05</v>
+      <c r="C3" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
@@ -5103,11 +5325,11 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n">
+      <c r="B4" s="46" t="n">
         <v>25.422</v>
       </c>
-      <c r="C4" s="52" t="n">
-        <v>28.684</v>
+      <c r="C4" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>99</v>
@@ -5119,11 +5341,14 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="B5" s="52" t="n">
+      <c r="B5" s="46" t="n">
         <v>55.025</v>
       </c>
-      <c r="C5" s="52" t="n">
-        <v>77.035</v>
+      <c r="C5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5132,11 +5357,11 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="B6" s="52" t="n">
-        <v>55.025</v>
-      </c>
-      <c r="C6" s="52" t="n">
-        <v>73.06100000000001</v>
+      <c r="B6" s="46" t="n">
+        <v>72.816</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5145,11 +5370,11 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="B7" s="52" t="n">
-        <v>55.025</v>
-      </c>
-      <c r="C7" s="52" t="n">
-        <v>73.06100000000001</v>
+      <c r="B7" s="46" t="n">
+        <v>83.726</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5158,11 +5383,11 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="B8" s="52" t="n">
-        <v>55.025</v>
-      </c>
-      <c r="C8" s="52" t="n">
-        <v>73.06100000000001</v>
+      <c r="B8" s="46" t="n">
+        <v>94.53700000000001</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5171,11 +5396,11 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n">
-        <v>55.025</v>
-      </c>
-      <c r="C9" s="52" t="n">
-        <v>73.06100000000001</v>
+      <c r="B9" s="46" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="C9" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5184,11 +5409,11 @@
           <t>M9</t>
         </is>
       </c>
-      <c r="B10" s="52" t="n">
-        <v>55.025</v>
-      </c>
-      <c r="C10" s="52" t="n">
-        <v>73.06100000000001</v>
+      <c r="B10" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/final_schedule.xlsx
+++ b/backend/final_schedule.xlsx
@@ -1583,31 +1583,31 @@
       </c>
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="N29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="O29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="P29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="Q29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="R29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="S29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="T29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="U29" s="20" t="n">
-        <v>0.06195467</v>
+        <v>0.062</v>
       </c>
       <c r="V29" s="11" t="n"/>
       <c r="W29" s="19" t="n"/>
@@ -1699,31 +1699,31 @@
       </c>
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="N32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="O32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="P32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="Q32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="R32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="S32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="U32" s="20" t="n">
-        <v>0.009296560000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V32" s="11" t="n"/>
       <c r="W32" s="19" t="n"/>
@@ -1759,31 +1759,31 @@
       </c>
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="N33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="O33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="Q33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="R33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="S33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="T33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="U33" s="20" t="n">
-        <v>0.00464822</v>
+        <v>0.0046</v>
       </c>
       <c r="V33" s="11" t="n"/>
       <c r="W33" s="19" t="n"/>
@@ -1875,31 +1875,31 @@
       </c>
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="N36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="O36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="P36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="Q36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="R36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="S36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="T36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="U36" s="20" t="n">
-        <v>0.00387356</v>
+        <v>0.0039</v>
       </c>
       <c r="V36" s="11" t="n"/>
       <c r="W36" s="19" t="n"/>
@@ -1935,31 +1935,31 @@
       </c>
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="N37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="O37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="P37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="Q37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="R37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="S37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="T37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="U37" s="20" t="n">
-        <v>0.00185933</v>
+        <v>0.0019</v>
       </c>
       <c r="V37" s="11" t="n"/>
       <c r="W37" s="19" t="n"/>
@@ -1995,31 +1995,31 @@
       </c>
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="N38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="O38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="P38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="Q38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="R38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="S38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="T38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="U38" s="20" t="n">
-        <v>0.01053611</v>
+        <v>0.0105</v>
       </c>
       <c r="V38" s="11" t="n"/>
       <c r="W38" s="19" t="n"/>
@@ -2055,31 +2055,31 @@
       </c>
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="N39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="O39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="P39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="Q39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="R39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="S39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="T39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="U39" s="20" t="n">
-        <v>0.005423</v>
+        <v>0.0054</v>
       </c>
       <c r="V39" s="11" t="n"/>
       <c r="W39" s="19" t="n"/>
@@ -2171,31 +2171,31 @@
       </c>
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="N42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="O42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="P42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="Q42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="R42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="S42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="T42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="U42" s="20" t="n">
-        <v>0.02479078</v>
+        <v>0.0248</v>
       </c>
       <c r="V42" s="11" t="n"/>
       <c r="W42" s="19" t="n"/>
@@ -2287,31 +2287,31 @@
       </c>
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="N45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="O45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="P45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="Q45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="R45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="S45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="T45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="U45" s="20" t="n">
-        <v>0.04648278</v>
+        <v>0.0465</v>
       </c>
       <c r="V45" s="11" t="n"/>
       <c r="W45" s="19" t="n"/>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="20" t="n">
-        <v>0.023706</v>
+        <v>0.0237</v>
       </c>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="17" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="20" t="n">
-        <v>0.023706</v>
+        <v>0.0237</v>
       </c>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="17" t="n"/>
@@ -2547,10 +2547,10 @@
       </c>
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="20" t="n">
-        <v>0.159058</v>
+        <v>0.1591</v>
       </c>
       <c r="N52" s="20" t="n">
-        <v>0.159058</v>
+        <v>0.1591</v>
       </c>
       <c r="O52" s="17" t="n"/>
       <c r="P52" s="17" t="n"/>
@@ -2589,22 +2589,22 @@
         <v>52997594.52</v>
       </c>
       <c r="K53" s="17" t="n">
-        <v>14.780848</v>
+        <v>14.780847</v>
       </c>
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="n"/>
       <c r="N53" s="17" t="n"/>
       <c r="O53" s="20" t="n">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="Q53" s="20" t="n">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="R53" s="20" t="n">
-        <v>3.695212</v>
+        <v>3.6952</v>
       </c>
       <c r="S53" s="17" t="n"/>
       <c r="T53" s="17" t="n"/>
@@ -2645,16 +2645,16 @@
       <c r="M54" s="17" t="n"/>
       <c r="N54" s="17" t="n"/>
       <c r="O54" s="20" t="n">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="P54" s="20" t="n">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="Q54" s="20" t="n">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="R54" s="20" t="n">
-        <v>0.18715525</v>
+        <v>0.1872</v>
       </c>
       <c r="S54" s="17" t="n"/>
       <c r="T54" s="17" t="n"/>
@@ -2694,16 +2694,16 @@
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="n"/>
       <c r="N55" s="20" t="n">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="O55" s="20" t="n">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="Q55" s="20" t="n">
-        <v>0.652855</v>
+        <v>0.6529</v>
       </c>
       <c r="R55" s="17" t="n"/>
       <c r="S55" s="17" t="n"/>
@@ -2739,14 +2739,14 @@
         <v>5398824</v>
       </c>
       <c r="K56" s="17" t="n">
-        <v>1.505714</v>
+        <v>1.505713</v>
       </c>
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="20" t="n">
-        <v>0.752857</v>
+        <v>0.7529</v>
       </c>
       <c r="N56" s="20" t="n">
-        <v>0.752857</v>
+        <v>0.7529</v>
       </c>
       <c r="O56" s="17" t="n"/>
       <c r="P56" s="17" t="n"/>
@@ -2793,16 +2793,16 @@
       <c r="O57" s="17" t="n"/>
       <c r="P57" s="17" t="n"/>
       <c r="Q57" s="20" t="n">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="R57" s="20" t="n">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="S57" s="20" t="n">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="T57" s="20" t="n">
-        <v>0.55906525</v>
+        <v>0.5591</v>
       </c>
       <c r="U57" s="17" t="n"/>
       <c r="V57" s="11" t="n"/>
@@ -2843,16 +2843,16 @@
       <c r="O58" s="17" t="n"/>
       <c r="P58" s="17" t="n"/>
       <c r="Q58" s="20" t="n">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="R58" s="20" t="n">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="S58" s="20" t="n">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="T58" s="20" t="n">
-        <v>0.013324</v>
+        <v>0.0133</v>
       </c>
       <c r="U58" s="17" t="n"/>
       <c r="V58" s="11" t="n"/>
@@ -2945,10 +2945,10 @@
       </c>
       <c r="L61" s="11" t="n"/>
       <c r="M61" s="20" t="n">
-        <v>0.110314</v>
+        <v>0.1103</v>
       </c>
       <c r="N61" s="20" t="n">
-        <v>0.110314</v>
+        <v>0.1103</v>
       </c>
       <c r="O61" s="17" t="n"/>
       <c r="P61" s="17" t="n"/>
@@ -2993,16 +2993,16 @@
       <c r="M62" s="17" t="n"/>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="20" t="n">
-        <v>1.70853283</v>
+        <v>1.7085</v>
       </c>
       <c r="P62" s="20" t="n">
-        <v>3.41706567</v>
+        <v>3.4171</v>
       </c>
       <c r="Q62" s="20" t="n">
-        <v>3.41706567</v>
+        <v>3.4171</v>
       </c>
       <c r="R62" s="20" t="n">
-        <v>1.70853283</v>
+        <v>1.7085</v>
       </c>
       <c r="S62" s="17" t="n"/>
       <c r="T62" s="17" t="n"/>
@@ -3043,16 +3043,16 @@
       <c r="M63" s="17" t="n"/>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="20" t="n">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="P63" s="20" t="n">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="Q63" s="20" t="n">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="R63" s="20" t="n">
-        <v>0.12746625</v>
+        <v>0.1275</v>
       </c>
       <c r="S63" s="17" t="n"/>
       <c r="T63" s="17" t="n"/>
@@ -3092,16 +3092,16 @@
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="17" t="n"/>
       <c r="N64" s="20" t="n">
-        <v>0.5159792</v>
+        <v>0.516</v>
       </c>
       <c r="O64" s="20" t="n">
-        <v>0.5159792</v>
+        <v>0.516</v>
       </c>
       <c r="P64" s="20" t="n">
-        <v>0.5159792</v>
+        <v>0.516</v>
       </c>
       <c r="Q64" s="20" t="n">
-        <v>0.1300014</v>
+        <v>0.13</v>
       </c>
       <c r="R64" s="17" t="n"/>
       <c r="S64" s="17" t="n"/>
@@ -3141,10 +3141,10 @@
       </c>
       <c r="L65" s="11" t="n"/>
       <c r="M65" s="20" t="n">
-        <v>0.55015167</v>
+        <v>0.5502</v>
       </c>
       <c r="N65" s="20" t="n">
-        <v>0.45365733</v>
+        <v>0.4537</v>
       </c>
       <c r="O65" s="17" t="n"/>
       <c r="P65" s="17" t="n"/>
@@ -3183,7 +3183,7 @@
         <v>5345496</v>
       </c>
       <c r="K66" s="17" t="n">
-        <v>1.490841</v>
+        <v>1.49084</v>
       </c>
       <c r="L66" s="11" t="n"/>
       <c r="M66" s="17" t="n"/>
@@ -3191,16 +3191,16 @@
       <c r="O66" s="17" t="n"/>
       <c r="P66" s="17" t="n"/>
       <c r="Q66" s="20" t="n">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="R66" s="20" t="n">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="S66" s="20" t="n">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="T66" s="20" t="n">
-        <v>0.37271025</v>
+        <v>0.3727</v>
       </c>
       <c r="U66" s="17" t="n"/>
       <c r="V66" s="11" t="n"/>
@@ -3241,16 +3241,16 @@
       <c r="O67" s="17" t="n"/>
       <c r="P67" s="17" t="n"/>
       <c r="Q67" s="20" t="n">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="R67" s="20" t="n">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="S67" s="20" t="n">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="T67" s="20" t="n">
-        <v>0.00888275</v>
+        <v>0.0089</v>
       </c>
       <c r="U67" s="17" t="n"/>
       <c r="V67" s="11" t="n"/>
@@ -3426,10 +3426,10 @@
       <c r="R72" s="17" t="n"/>
       <c r="S72" s="17" t="n"/>
       <c r="T72" s="20" t="n">
-        <v>0.238524</v>
+        <v>0.2385</v>
       </c>
       <c r="U72" s="20" t="n">
-        <v>0.119262</v>
+        <v>0.1193</v>
       </c>
       <c r="V72" s="11" t="n"/>
       <c r="W72" s="19" t="n"/>
@@ -3472,10 +3472,10 @@
       <c r="R73" s="17" t="n"/>
       <c r="S73" s="17" t="n"/>
       <c r="T73" s="20" t="n">
-        <v>0.06340867</v>
+        <v>0.0634</v>
       </c>
       <c r="U73" s="20" t="n">
-        <v>0.03170433</v>
+        <v>0.0317</v>
       </c>
       <c r="V73" s="11" t="n"/>
       <c r="W73" s="19" t="n"/>
@@ -3518,10 +3518,10 @@
       <c r="R74" s="17" t="n"/>
       <c r="S74" s="17" t="n"/>
       <c r="T74" s="20" t="n">
-        <v>0.022808</v>
+        <v>0.0228</v>
       </c>
       <c r="U74" s="20" t="n">
-        <v>0.011404</v>
+        <v>0.0114</v>
       </c>
       <c r="V74" s="11" t="n"/>
       <c r="W74" s="19" t="n"/>
@@ -3564,10 +3564,10 @@
       <c r="R75" s="17" t="n"/>
       <c r="S75" s="17" t="n"/>
       <c r="T75" s="20" t="n">
-        <v>0.16730133</v>
+        <v>0.1673</v>
       </c>
       <c r="U75" s="20" t="n">
-        <v>0.08365067</v>
+        <v>0.0837</v>
       </c>
       <c r="V75" s="11" t="n"/>
       <c r="W75" s="19" t="n"/>
@@ -3610,10 +3610,10 @@
       <c r="R76" s="17" t="n"/>
       <c r="S76" s="17" t="n"/>
       <c r="T76" s="20" t="n">
-        <v>0.02368733</v>
+        <v>0.0237</v>
       </c>
       <c r="U76" s="20" t="n">
-        <v>0.01184367</v>
+        <v>0.0118</v>
       </c>
       <c r="V76" s="11" t="n"/>
       <c r="W76" s="19" t="n"/>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="L79" s="11" t="n"/>
       <c r="M79" s="20" t="n">
-        <v>0.315455</v>
+        <v>0.3155</v>
       </c>
       <c r="N79" s="17" t="n"/>
       <c r="O79" s="17" t="n"/>
@@ -3736,20 +3736,20 @@
         </is>
       </c>
       <c r="H80" s="17" t="n">
-        <v>135.74925</v>
+        <v>135.7493</v>
       </c>
       <c r="I80" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>746620.8749999999</v>
+        <v>746621.15</v>
       </c>
       <c r="K80" s="17" t="n">
         <v>0.20823</v>
       </c>
       <c r="L80" s="11" t="n"/>
       <c r="M80" s="20" t="n">
-        <v>0.20823</v>
+        <v>0.2082</v>
       </c>
       <c r="N80" s="17" t="n"/>
       <c r="O80" s="17" t="n"/>
@@ -3780,27 +3780,27 @@
         </is>
       </c>
       <c r="H81" s="17" t="n">
-        <v>135.74925</v>
+        <v>135.7493</v>
       </c>
       <c r="I81" s="18" t="n">
         <v>255550</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>34690720.8375</v>
+        <v>34690733.615</v>
       </c>
       <c r="K81" s="17" t="n">
-        <v>9.675122999999999</v>
+        <v>9.675126000000001</v>
       </c>
       <c r="L81" s="11" t="n"/>
       <c r="M81" s="17" t="n"/>
       <c r="N81" s="20" t="n">
-        <v>1.20939038</v>
+        <v>1.2094</v>
       </c>
       <c r="O81" s="20" t="n">
-        <v>4.78931444</v>
+        <v>4.7893</v>
       </c>
       <c r="P81" s="20" t="n">
-        <v>3.67641818</v>
+        <v>3.6764</v>
       </c>
       <c r="Q81" s="17" t="n"/>
       <c r="R81" s="17" t="n"/>
@@ -3842,10 +3842,10 @@
       <c r="L82" s="11" t="n"/>
       <c r="M82" s="17" t="n"/>
       <c r="N82" s="20" t="n">
-        <v>0.2472935</v>
+        <v>0.2473</v>
       </c>
       <c r="O82" s="20" t="n">
-        <v>0.2472935</v>
+        <v>0.2473</v>
       </c>
       <c r="P82" s="17" t="n"/>
       <c r="Q82" s="17" t="n"/>
@@ -3891,13 +3891,13 @@
       <c r="O83" s="17" t="n"/>
       <c r="P83" s="17" t="n"/>
       <c r="Q83" s="20" t="n">
-        <v>0.1845066</v>
+        <v>0.1845</v>
       </c>
       <c r="R83" s="20" t="n">
-        <v>0.34594988</v>
+        <v>0.3459</v>
       </c>
       <c r="S83" s="20" t="n">
-        <v>2.23714252</v>
+        <v>2.2371</v>
       </c>
       <c r="T83" s="17" t="n"/>
       <c r="U83" s="17" t="n"/>
@@ -3936,10 +3936,10 @@
       <c r="L84" s="11" t="n"/>
       <c r="M84" s="17" t="n"/>
       <c r="N84" s="20" t="n">
-        <v>0.5019045</v>
+        <v>0.5019</v>
       </c>
       <c r="O84" s="20" t="n">
-        <v>0.5019045</v>
+        <v>0.5019</v>
       </c>
       <c r="P84" s="17" t="n"/>
       <c r="Q84" s="17" t="n"/>
@@ -3977,7 +3977,7 @@
         <v>5345496</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>1.490841</v>
+        <v>1.49084</v>
       </c>
       <c r="L85" s="11" t="n"/>
       <c r="M85" s="17" t="n"/>
@@ -3988,10 +3988,10 @@
       <c r="R85" s="17" t="n"/>
       <c r="S85" s="17" t="n"/>
       <c r="T85" s="20" t="n">
-        <v>0.7454205</v>
+        <v>0.7454</v>
       </c>
       <c r="U85" s="20" t="n">
-        <v>0.7454205</v>
+        <v>0.7454</v>
       </c>
       <c r="V85" s="11" t="n"/>
       <c r="W85" s="19" t="n"/>
@@ -4034,10 +4034,10 @@
       <c r="R86" s="17" t="n"/>
       <c r="S86" s="17" t="n"/>
       <c r="T86" s="20" t="n">
-        <v>0.0177655</v>
+        <v>0.0178</v>
       </c>
       <c r="U86" s="20" t="n">
-        <v>0.0177655</v>
+        <v>0.017</v>
       </c>
       <c r="V86" s="11" t="n"/>
       <c r="W86" s="19" t="n"/>
@@ -4162,7 +4162,7 @@
       <c r="L90" s="11" t="n"/>
       <c r="M90" s="17" t="n"/>
       <c r="N90" s="20" t="n">
-        <v>0.63532</v>
+        <v>0.6353</v>
       </c>
       <c r="O90" s="17" t="n"/>
       <c r="P90" s="17" t="n"/>
@@ -4201,25 +4201,25 @@
         <v>61584381.18</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>17.175673</v>
+        <v>17.175672</v>
       </c>
       <c r="L91" s="11" t="n"/>
       <c r="M91" s="17" t="n"/>
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="20" t="n">
-        <v>0.95420406</v>
+        <v>0.9542</v>
       </c>
       <c r="P91" s="20" t="n">
-        <v>5.18136414</v>
+        <v>5.1814</v>
       </c>
       <c r="Q91" s="20" t="n">
-        <v>4.29391825</v>
+        <v>4.2939</v>
       </c>
       <c r="R91" s="20" t="n">
-        <v>3.37309328</v>
+        <v>3.3731</v>
       </c>
       <c r="S91" s="20" t="n">
-        <v>3.37309328</v>
+        <v>3.3731</v>
       </c>
       <c r="T91" s="17" t="n"/>
       <c r="U91" s="17" t="n"/>
@@ -4259,19 +4259,19 @@
       <c r="M92" s="17" t="n"/>
       <c r="N92" s="17" t="n"/>
       <c r="O92" s="20" t="n">
-        <v>0.74386839</v>
+        <v>0.7439</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>9.231605220000001</v>
+        <v>9.2316</v>
       </c>
       <c r="Q92" s="20" t="n">
-        <v>3.34740775</v>
+        <v>3.3474</v>
       </c>
       <c r="R92" s="20" t="n">
-        <v>0.03337482</v>
+        <v>0.0334</v>
       </c>
       <c r="S92" s="20" t="n">
-        <v>0.03337482</v>
+        <v>0.0334</v>
       </c>
       <c r="T92" s="17" t="n"/>
       <c r="U92" s="17" t="n"/>
@@ -4311,19 +4311,19 @@
       <c r="M93" s="17" t="n"/>
       <c r="N93" s="17" t="n"/>
       <c r="O93" s="20" t="n">
-        <v>0.15502667</v>
+        <v>0.155</v>
       </c>
       <c r="P93" s="20" t="n">
-        <v>0.31005333</v>
+        <v>0.3101</v>
       </c>
       <c r="Q93" s="20" t="n">
-        <v>0.23254</v>
+        <v>0.2325</v>
       </c>
       <c r="R93" s="20" t="n">
-        <v>0.11627</v>
+        <v>0.1163</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>0.11627</v>
+        <v>0.1163</v>
       </c>
       <c r="T93" s="17" t="n"/>
       <c r="U93" s="17" t="n"/>
@@ -4363,19 +4363,19 @@
       <c r="M94" s="17" t="n"/>
       <c r="N94" s="17" t="n"/>
       <c r="O94" s="20" t="n">
-        <v>0.39988625</v>
+        <v>0.3999</v>
       </c>
       <c r="P94" s="20" t="n">
-        <v>0.39988625</v>
+        <v>0.3999</v>
       </c>
       <c r="Q94" s="20" t="n">
-        <v>0.39988625</v>
+        <v>0.3999</v>
       </c>
       <c r="R94" s="20" t="n">
-        <v>0.19994313</v>
+        <v>0.1999</v>
       </c>
       <c r="S94" s="20" t="n">
-        <v>0.19994313</v>
+        <v>0.1999</v>
       </c>
       <c r="T94" s="17" t="n"/>
       <c r="U94" s="17" t="n"/>
@@ -4414,13 +4414,13 @@
       <c r="L95" s="11" t="n"/>
       <c r="M95" s="17" t="n"/>
       <c r="N95" s="20" t="n">
-        <v>1.22339225</v>
+        <v>1.2234</v>
       </c>
       <c r="O95" s="20" t="n">
-        <v>1.63118967</v>
+        <v>1.6312</v>
       </c>
       <c r="P95" s="20" t="n">
-        <v>2.03898708</v>
+        <v>2.039</v>
       </c>
       <c r="Q95" s="17" t="n"/>
       <c r="R95" s="17" t="n"/>
@@ -4467,10 +4467,10 @@
       <c r="Q96" s="17" t="n"/>
       <c r="R96" s="17" t="n"/>
       <c r="S96" s="20" t="n">
-        <v>0.6817879999999999</v>
+        <v>0.6818</v>
       </c>
       <c r="T96" s="20" t="n">
-        <v>0.340894</v>
+        <v>0.3409</v>
       </c>
       <c r="U96" s="17" t="n"/>
       <c r="V96" s="11" t="n"/>
@@ -4503,7 +4503,7 @@
         <v>16036488</v>
       </c>
       <c r="K97" s="17" t="n">
-        <v>4.472522</v>
+        <v>4.472521</v>
       </c>
       <c r="L97" s="11" t="n"/>
       <c r="M97" s="17" t="n"/>
@@ -4513,10 +4513,10 @@
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="17" t="n"/>
       <c r="S97" s="20" t="n">
-        <v>2.98168133</v>
+        <v>2.9817</v>
       </c>
       <c r="T97" s="20" t="n">
-        <v>1.49084067</v>
+        <v>1.4908</v>
       </c>
       <c r="U97" s="17" t="n"/>
       <c r="V97" s="11" t="n"/>
@@ -4559,10 +4559,10 @@
       <c r="Q98" s="17" t="n"/>
       <c r="R98" s="17" t="n"/>
       <c r="S98" s="20" t="n">
-        <v>0.04737467</v>
+        <v>0.0474</v>
       </c>
       <c r="T98" s="20" t="n">
-        <v>0.02368733</v>
+        <v>0.0237</v>
       </c>
       <c r="U98" s="17" t="n"/>
       <c r="V98" s="11" t="n"/>
@@ -4605,10 +4605,10 @@
       <c r="Q99" s="17" t="n"/>
       <c r="R99" s="17" t="n"/>
       <c r="S99" s="20" t="n">
-        <v>0.017388</v>
+        <v>0.017</v>
       </c>
       <c r="T99" s="20" t="n">
-        <v>0.008694</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U99" s="17" t="n"/>
       <c r="V99" s="11" t="n"/>
@@ -4783,7 +4783,7 @@
       <c r="K106" s="33" t="n"/>
       <c r="L106" s="28" t="n"/>
       <c r="M106" s="34" t="n">
-        <v>2.312</v>
+        <v>2.313</v>
       </c>
       <c r="N106" s="34" t="n">
         <v>6.631</v>
@@ -4807,7 +4807,7 @@
         <v>4.274</v>
       </c>
       <c r="U106" s="34" t="n">
-        <v>1.19</v>
+        <v>1.189</v>
       </c>
       <c r="V106" s="28" t="n"/>
       <c r="W106" s="29" t="n"/>
@@ -4829,28 +4829,28 @@
       <c r="K107" s="33" t="n"/>
       <c r="L107" s="28" t="n"/>
       <c r="M107" s="34" t="n">
-        <v>2.312</v>
+        <v>2.313</v>
       </c>
       <c r="N107" s="34" t="n">
-        <v>8.943</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="O107" s="34" t="n">
         <v>25.422</v>
       </c>
       <c r="P107" s="34" t="n">
-        <v>55.025</v>
+        <v>55.026</v>
       </c>
       <c r="Q107" s="34" t="n">
-        <v>72.816</v>
+        <v>72.81699999999999</v>
       </c>
       <c r="R107" s="34" t="n">
-        <v>83.726</v>
+        <v>83.727</v>
       </c>
       <c r="S107" s="34" t="n">
         <v>94.53700000000001</v>
       </c>
       <c r="T107" s="34" t="n">
-        <v>98.81</v>
+        <v>98.81100000000001</v>
       </c>
       <c r="U107" s="34" t="n">
         <v>100</v>
@@ -4975,28 +4975,28 @@
       <c r="K110" s="33" t="n"/>
       <c r="L110" s="37" t="n"/>
       <c r="M110" s="34" t="n">
-        <v>-2.312</v>
+        <v>-2.313</v>
       </c>
       <c r="N110" s="34" t="n">
-        <v>-8.943</v>
+        <v>-8.944000000000001</v>
       </c>
       <c r="O110" s="34" t="n">
         <v>-25.422</v>
       </c>
       <c r="P110" s="34" t="n">
-        <v>-55.025</v>
+        <v>-55.026</v>
       </c>
       <c r="Q110" s="34" t="n">
-        <v>-72.816</v>
+        <v>-72.81699999999999</v>
       </c>
       <c r="R110" s="34" t="n">
-        <v>-83.726</v>
+        <v>-83.727</v>
       </c>
       <c r="S110" s="34" t="n">
         <v>-94.53700000000001</v>
       </c>
       <c r="T110" s="34" t="n">
-        <v>-98.81</v>
+        <v>-98.81100000000001</v>
       </c>
       <c r="U110" s="34" t="n">
         <v>-100</v>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="B2" s="46" t="n">
-        <v>2.312</v>
+        <v>2.313</v>
       </c>
       <c r="C2" s="46" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="B3" s="46" t="n">
-        <v>8.943</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="C3" s="46" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="B5" s="46" t="n">
-        <v>55.025</v>
+        <v>55.026</v>
       </c>
       <c r="C5" s="46" t="n">
         <v>0</v>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="B6" s="46" t="n">
-        <v>72.816</v>
+        <v>72.81699999999999</v>
       </c>
       <c r="C6" s="46" t="n">
         <v>0</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="B7" s="46" t="n">
-        <v>83.726</v>
+        <v>83.727</v>
       </c>
       <c r="C7" s="46" t="n">
         <v>0</v>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="B9" s="46" t="n">
-        <v>98.81</v>
+        <v>98.81100000000001</v>
       </c>
       <c r="C9" s="46" t="n">
         <v>0</v>
